--- a/ShopFlow API testCase.xlsx
+++ b/ShopFlow API testCase.xlsx
@@ -1,23 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\QA Engineer\ShopFlow API\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4626FD87-58F7-40B3-A90A-71A4281AC8DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A689C756-17E4-4D43-A4C0-E0B148606382}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12000" yWindow="0" windowWidth="12000" windowHeight="13500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13740" tabRatio="650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Version History" sheetId="1" r:id="rId1"/>
     <sheet name="Test Scenario" sheetId="2" r:id="rId2"/>
     <sheet name="Users" sheetId="3" r:id="rId3"/>
+    <sheet name="Products" sheetId="4" r:id="rId4"/>
+    <sheet name="Orders" sheetId="5" r:id="rId5"/>
+    <sheet name="Reviews" sheetId="6" r:id="rId6"/>
+    <sheet name="Carts" sheetId="7" r:id="rId7"/>
+    <sheet name="Coupons" sheetId="8" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="223">
   <si>
     <t>Project Name</t>
   </si>
@@ -209,45 +214,584 @@
     <t>User exists</t>
   </si>
   <si>
+    <t>Expected Status Code</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>User Details Returned</t>
+  </si>
+  <si>
+    <t>valid user payload</t>
+  </si>
+  <si>
+    <t>missing email</t>
+  </si>
+  <si>
+    <t>userid=1</t>
+  </si>
+  <si>
+    <t>invalid user id</t>
+  </si>
+  <si>
+    <t>End Point</t>
+  </si>
+  <si>
+    <t>Method</t>
+  </si>
+  <si>
+    <t>POST</t>
+  </si>
+  <si>
+    <t>GET</t>
+  </si>
+  <si>
+    <t>api/users</t>
+  </si>
+  <si>
+    <t>api/users/1</t>
+  </si>
+  <si>
+    <t>api/user/999</t>
+  </si>
+  <si>
+    <t>Create user with name shorter than 3 chars</t>
+  </si>
+  <si>
+    <t>Create user with invalid email format</t>
+  </si>
+  <si>
+    <t>Create user with duplicate email</t>
+  </si>
+  <si>
+    <t>Create user with invalid phone number</t>
+  </si>
+  <si>
+    <t>Create user with invalid role</t>
+  </si>
+  <si>
+    <t>/api/users</t>
+  </si>
+  <si>
+    <t>TC_User_006</t>
+  </si>
+  <si>
+    <t>TC_User_007</t>
+  </si>
+  <si>
+    <t>TC_User_008</t>
+  </si>
+  <si>
+    <t>TC_User_009</t>
+  </si>
+  <si>
+    <t>TC_User_010</t>
+  </si>
+  <si>
+    <t>TC_User_011</t>
+  </si>
+  <si>
+    <t>TC_User_012</t>
+  </si>
+  <si>
+    <t>Retrieve all users</t>
+  </si>
+  <si>
+    <t>Delete existing user</t>
+  </si>
+  <si>
+    <t>DELETE</t>
+  </si>
+  <si>
+    <t>1. Send PATCH /api/users/1
+2. Verify status 200
+3. Verify phone updated</t>
+  </si>
+  <si>
+    <t>1. Send GET /api/users
+2. Verify status 200
+3. Verify response is an array</t>
+  </si>
+  <si>
+    <t>1. Send POST /api/users with role=superuser
+2. Verify status 400
+3. Verify error message</t>
+  </si>
+  <si>
+    <t>1. Send POST /api/users with invalid phone
+2. Verify status 400
+3. Verify error message</t>
+  </si>
+  <si>
+    <t>1. Send POST /api/users with existing email
+2. Verify status 400
+3. Verify error message</t>
+  </si>
+  <si>
+    <t>1. Send POST /api/users with bad email
+2. Verify status 400
+3. Verify error message</t>
+  </si>
+  <si>
+    <t>1. Send POST /api/users with name='Jo'
+2. Verify status 400
+3. Verify error message</t>
+  </si>
+  <si>
+    <t>400</t>
+  </si>
+  <si>
+    <t>Test Type</t>
+  </si>
+  <si>
+    <t>Positive</t>
+  </si>
+  <si>
+    <t>Products</t>
+  </si>
+  <si>
+    <t>/api/products</t>
+  </si>
+  <si>
+    <t>Create product with valid data</t>
+  </si>
+  <si>
+    <t>API running</t>
+  </si>
+  <si>
+    <t>1. Send POST /api/products
+2. Verify status 201
+3. Verify id in response</t>
+  </si>
+  <si>
+    <t>Product created successfully</t>
+  </si>
+  <si>
+    <t>201</t>
+  </si>
+  <si>
+    <t>Create product with negative price</t>
+  </si>
+  <si>
+    <t>{"name":"Bad Item","price":-5,"categoryId":1,"stock":10}</t>
+  </si>
+  <si>
+    <t>1. Send POST /api/products with negative price
+2. Verify behaviour</t>
+  </si>
+  <si>
+    <t>Validation error (or note: json-server permissive)</t>
+  </si>
+  <si>
+    <t>Negative</t>
+  </si>
+  <si>
+    <t>Retrieve all products</t>
+  </si>
+  <si>
+    <t>Products exist</t>
+  </si>
+  <si>
+    <t>No body required</t>
+  </si>
+  <si>
+    <t>1. Send GET /api/products
+2. Verify status 200
+3. Verify array returned</t>
+  </si>
+  <si>
+    <t>Array of product objects returned</t>
+  </si>
+  <si>
+    <t>200</t>
+  </si>
+  <si>
+    <t>/api/products/1</t>
+  </si>
+  <si>
+    <t>Retrieve product by valid ID</t>
+  </si>
+  <si>
+    <t>Product id=1 exists</t>
+  </si>
+  <si>
+    <t>productId = 1</t>
+  </si>
+  <si>
+    <t>1. Send GET /api/products/1
+2. Verify status 200
+3. Verify id=1 in response</t>
+  </si>
+  <si>
+    <t>Product details returned</t>
+  </si>
+  <si>
+    <t>/api/products/9999</t>
+  </si>
+  <si>
+    <t>Retrieve product by invalid ID</t>
+  </si>
+  <si>
+    <t>productId = 9999</t>
+  </si>
+  <si>
+    <t>1. Send GET /api/products/9999
+2. Verify status 404</t>
+  </si>
+  <si>
+    <t>Product not found</t>
+  </si>
+  <si>
+    <t>404</t>
+  </si>
+  <si>
+    <t>/api/products?status=active</t>
+  </si>
+  <si>
+    <t>Filter active products</t>
+  </si>
+  <si>
+    <t>Active products exist</t>
+  </si>
+  <si>
+    <t>status = active</t>
+  </si>
+  <si>
+    <t>1. Send GET /api/products?status=active
+2. Verify all results have status=active</t>
+  </si>
+  <si>
+    <t>Only active products returned</t>
+  </si>
+  <si>
+    <t>/api/products?status=out_of_stock</t>
+  </si>
+  <si>
+    <t>Filter out-of-stock products</t>
+  </si>
+  <si>
+    <t>OOS product exists</t>
+  </si>
+  <si>
+    <t>status = out_of_stock</t>
+  </si>
+  <si>
+    <t>1. Send GET /api/products?status=out_of_stock
+2. Verify results</t>
+  </si>
+  <si>
+    <t>Only out-of-stock products returned</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>/api/products?categoryId=1</t>
+  </si>
+  <si>
+    <t>Filter products by category</t>
+  </si>
+  <si>
+    <t>Products in cat 1 exist</t>
+  </si>
+  <si>
+    <t>categoryId = 1</t>
+  </si>
+  <si>
+    <t>1. Send GET /api/products?categoryId=1
+2. Verify all results have categoryId=1</t>
+  </si>
+  <si>
+    <t>Only products in category 1 returned</t>
+  </si>
+  <si>
+    <t>/api/products?_sort=price&amp;_order=asc</t>
+  </si>
+  <si>
+    <t>Sort products by price ascending</t>
+  </si>
+  <si>
+    <t>_sort=price&amp;_order=asc</t>
+  </si>
+  <si>
+    <t>1. Send GET with sort params
+2. Verify prices are in ascending order</t>
+  </si>
+  <si>
+    <t>Products sorted by price low to high</t>
+  </si>
+  <si>
+    <t>/api/products?_sort=price&amp;_order=desc</t>
+  </si>
+  <si>
+    <t>Sort products by price descending</t>
+  </si>
+  <si>
+    <t>_sort=price&amp;_order=desc</t>
+  </si>
+  <si>
+    <t>1. Send GET with sort params
+2. Verify prices are in descending order</t>
+  </si>
+  <si>
+    <t>Products sorted by price high to low</t>
+  </si>
+  <si>
+    <t>/api/products?_page=1&amp;_limit=3</t>
+  </si>
+  <si>
+    <t>Paginate products</t>
+  </si>
+  <si>
+    <t>More than 3 products exist</t>
+  </si>
+  <si>
+    <t>_page=1&amp;_limit=3</t>
+  </si>
+  <si>
+    <t>1. Send GET with pagination params
+2. Verify exactly 3 results returned</t>
+  </si>
+  <si>
+    <t>3 products returned</t>
+  </si>
+  <si>
+    <t>/api/products?name_like=Headphones</t>
+  </si>
+  <si>
+    <t>Search products by name</t>
+  </si>
+  <si>
+    <t>Headphone product exists</t>
+  </si>
+  <si>
+    <t>name_like = Headphones</t>
+  </si>
+  <si>
+    <t>1. Send GET with name_like param
+2. Verify matching products returned</t>
+  </si>
+  <si>
+    <t>Products with matching name returned</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>PATCH</t>
+  </si>
+  <si>
+    <t>Update product price</t>
+  </si>
+  <si>
+    <t>{"price":129.99}</t>
+  </si>
+  <si>
+    <t>1. Send PATCH /api/products/1
+2. Verify status 200
+3. Verify price updated</t>
+  </si>
+  <si>
+    <t>Product price updated</t>
+  </si>
+  <si>
+    <t>Update product stock to zero</t>
+  </si>
+  <si>
+    <t>{"stock":0}</t>
+  </si>
+  <si>
+    <t>1. Send PATCH /api/products/1 with stock=0
+2. Verify status 200</t>
+  </si>
+  <si>
+    <t>Stock updated to 0</t>
+  </si>
+  <si>
+    <t>/api/products/7</t>
+  </si>
+  <si>
+    <t>Delete a product</t>
+  </si>
+  <si>
+    <t>Product id=7 exists</t>
+  </si>
+  <si>
+    <t>productId = 7</t>
+  </si>
+  <si>
+    <t>1. Send DELETE /api/products/7
+2. Verify status 200
+3. Confirm GET returns 404</t>
+  </si>
+  <si>
+    <t>Product deleted successfully</t>
+  </si>
+  <si>
+    <t>TC_Products_001</t>
+  </si>
+  <si>
+    <t>TC_Products_002</t>
+  </si>
+  <si>
+    <t>TC_Products_003</t>
+  </si>
+  <si>
+    <t>TC_Products_004</t>
+  </si>
+  <si>
+    <t>TC_Products_005</t>
+  </si>
+  <si>
+    <t>TC_Products_006</t>
+  </si>
+  <si>
+    <t>TC_Products_007</t>
+  </si>
+  <si>
+    <t>TC_Products_008</t>
+  </si>
+  <si>
+    <t>TC_Products_009</t>
+  </si>
+  <si>
+    <t>TC_Products_010</t>
+  </si>
+  <si>
+    <t>TC_Products_011</t>
+  </si>
+  <si>
+    <t>TC_Products_012</t>
+  </si>
+  <si>
+    <t>TC_Products_013</t>
+  </si>
+  <si>
+    <t>TC_Products_014</t>
+  </si>
+  <si>
+    <t>TC_Products_015</t>
+  </si>
+  <si>
+    <t>{
+  "error":"Email is required"
+}</t>
+  </si>
+  <si>
+    <t>Created Successfully</t>
+  </si>
+  <si>
+    <t>{}</t>
+  </si>
+  <si>
+    <t>{
+    "name":"jo",
+    "email":"{{useremail}}",
+    "phone":"{{usernumber}}",
+    "role":"customer"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "error": "Name must be at least 3 characters"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "name":"{{username}}",
+    "email":"user-gmail.com",
+    "phone":"{{usernumber}}",
+    "role":"customer"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "error": "Invalid email format"
+}</t>
+  </si>
+  <si>
     <t>1. Send POST request
-2. Validate Response</t>
-  </si>
-  <si>
-    <t>Expected Status Code</t>
-  </si>
-  <si>
-    <t>High</t>
-  </si>
-  <si>
-    <t>User Created Successfully</t>
-  </si>
-  <si>
-    <t>Validation Error Returned</t>
-  </si>
-  <si>
-    <t>User Details Returned</t>
-  </si>
-  <si>
-    <t>User Not Found</t>
-  </si>
-  <si>
-    <t>valid user payload</t>
-  </si>
-  <si>
-    <t>missing email</t>
-  </si>
-  <si>
-    <t>userid=1</t>
-  </si>
-  <si>
-    <t>invalid user id</t>
+2. Verify Successful Message
+3. Verify Status 201</t>
+  </si>
+  <si>
+    <t>1. Send POST request
+2. Verify Status 400
+3. Verify error message</t>
+  </si>
+  <si>
+    <t>1. Send GET request
+2. Verify Status 200</t>
+  </si>
+  <si>
+    <t>1. Send GET request
+2. Verify Status 404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+    "name":"{{username}}",
+    "email":"alice@example.com",
+    "phone":"{{usernumber}}",
+    "role":"customer"
+}
+</t>
+  </si>
+  <si>
+    <t>{
+    "error": "Email already exists"
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+    "name":"{{username}}",
+    "email":"{{useremail}}",
+    "phone":"5647",
+    "role":"customer"
+}
+</t>
+  </si>
+  <si>
+    <t>{
+    "error": "Invalid phone number"
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{
+    "name":"{{username}}",
+    "email":"{{useremail}}",
+    "phone":"{{usernumber}}",
+    "role": "player"
+}
+</t>
+  </si>
+  <si>
+    <t>{
+    "error": "Invalid role"
+}</t>
+  </si>
+  <si>
+    <t>update user Phone</t>
+  </si>
+  <si>
+    <t>1. Send DELETE /api/users/6
+2. Verify status 200
+3. Confirm with GET</t>
+  </si>
+  <si>
+    <t>{
+    "phone":"{{usernumber}}"
+}</t>
+  </si>
+  <si>
+    <t>NA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -281,8 +825,40 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -291,13 +867,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="3" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.59999389629810485"/>
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -330,27 +912,68 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -641,34 +1264,34 @@
   </cols>
   <sheetData>
     <row r="13" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E13" s="1"/>
-      <c r="F13" s="2" t="s">
+      <c r="E13" s="26"/>
+      <c r="F13" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="G13" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="1"/>
+      <c r="H13" s="26"/>
     </row>
     <row r="14" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E14" s="1"/>
-      <c r="F14" s="2" t="s">
+      <c r="E14" s="26"/>
+      <c r="F14" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="G14" s="2" t="s">
+      <c r="G14" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="H14" s="1"/>
+      <c r="H14" s="26"/>
     </row>
     <row r="15" spans="5:8" x14ac:dyDescent="0.25">
-      <c r="E15" s="1"/>
-      <c r="F15" s="2" t="s">
+      <c r="E15" s="26"/>
+      <c r="F15" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="G15" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="H15" s="1"/>
+      <c r="H15" s="26"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -688,238 +1311,256 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="24" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="24" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="3"/>
+      <c r="B3" s="24"/>
     </row>
     <row r="4" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="24" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="24" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="24" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="25" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E10" s="5"/>
+      <c r="E10" s="1"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E11" s="5"/>
+      <c r="E11" s="1"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E12" s="5"/>
+      <c r="E12" s="1"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E13" s="5"/>
+      <c r="E13" s="1"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E14" s="5"/>
+      <c r="E14" s="1"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E15" s="5"/>
+      <c r="E15" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="A10" location="Users!A1" display="TS_001_Users" xr:uid="{6312A61C-3A4F-40D4-A2A7-F69AD6FBA0BE}"/>
+    <hyperlink ref="A11" location="Products!A1" display="TS_002_Products" xr:uid="{2CAC6549-A713-4991-A1FC-37A44CE00843}"/>
+    <hyperlink ref="A12" location="Orders!A1" display="TS_003_Orders" xr:uid="{D7DEB18D-F1DC-4BC4-BA61-963FFCC4CABF}"/>
+    <hyperlink ref="A13" location="Reviews!A1" display="TS_004_Reviews" xr:uid="{196BC95E-DCF1-4492-A921-E36071DB2742}"/>
+    <hyperlink ref="A14" location="Carts!A1" display="TS_005_Carts" xr:uid="{F48114BC-3927-43CA-B6F2-67E11AFB654D}"/>
+    <hyperlink ref="A15" location="Coupons!A1" display="TS_006_Coupons" xr:uid="{7948A9F3-7E2B-4DA1-AD0E-D83EFF568A4E}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71436715-D8AD-482B-9A90-C2427058D2B6}">
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="26.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="22" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.5703125" style="21" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="34.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="36" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.42578125" customWidth="1"/>
+    <col min="9" max="9" width="21.42578125" style="18" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="E1" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="F1" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="G1" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="H1" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="I1" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="H1" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="I1" s="6" t="s">
+      <c r="J1" s="23" t="s">
+        <v>60</v>
+      </c>
+      <c r="K1" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="L1" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="K1" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="L1" s="6" t="s">
+      <c r="M1" s="23" t="s">
+        <v>98</v>
+      </c>
+      <c r="N1" s="23" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
       <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-    </row>
-    <row r="3" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="11"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="7"/>
+      <c r="M2" s="7"/>
+      <c r="N2" s="7"/>
+    </row>
+    <row r="3" spans="1:14" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>48</v>
       </c>
@@ -927,31 +1568,39 @@
         <v>53</v>
       </c>
       <c r="C3" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E3" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="F3" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="E3" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="9" t="s">
+        <v>209</v>
+      </c>
+      <c r="H3" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="H3" s="10">
+      <c r="I3" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="J3" s="5">
         <v>201</v>
       </c>
-      <c r="I3" s="8"/>
-      <c r="J3" s="10" t="s">
-        <v>62</v>
-      </c>
       <c r="K3" s="8"/>
-      <c r="L3" s="8"/>
-    </row>
-    <row r="4" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="L3" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="M3" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="N3" s="8"/>
+    </row>
+    <row r="4" spans="1:14" ht="51" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>49</v>
       </c>
@@ -959,31 +1608,39 @@
         <v>53</v>
       </c>
       <c r="C4" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E4" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="F4" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="E4" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="G4" s="8" t="s">
+      <c r="G4" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="H4" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="H4" s="10">
+      <c r="I4" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="J4" s="5">
         <v>400</v>
       </c>
-      <c r="I4" s="8"/>
-      <c r="J4" s="10" t="s">
-        <v>62</v>
-      </c>
       <c r="K4" s="8"/>
-      <c r="L4" s="8"/>
-    </row>
-    <row r="5" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="L4" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="M4" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="N4" s="8"/>
+    </row>
+    <row r="5" spans="1:14" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>50</v>
       </c>
@@ -991,31 +1648,39 @@
         <v>53</v>
       </c>
       <c r="C5" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="E5" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="F5" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="E5" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="G5" s="8" t="s">
+      <c r="G5" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="H5" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="H5" s="10">
+      <c r="I5" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="J5" s="5">
         <v>200</v>
       </c>
-      <c r="I5" s="8"/>
-      <c r="J5" s="10" t="s">
-        <v>62</v>
-      </c>
       <c r="K5" s="8"/>
-      <c r="L5" s="8"/>
-    </row>
-    <row r="6" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="L5" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="M5" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="N5" s="8"/>
+    </row>
+    <row r="6" spans="1:14" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>51</v>
       </c>
@@ -1023,187 +1688,347 @@
         <v>53</v>
       </c>
       <c r="C6" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="E6" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="F6" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="E6" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="G6" s="8" t="s">
+      <c r="G6" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="H6" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="H6" s="10">
+      <c r="I6" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="J6" s="5">
         <v>404</v>
       </c>
-      <c r="I6" s="8"/>
-      <c r="J6" s="10" t="s">
-        <v>62</v>
-      </c>
       <c r="K6" s="8"/>
-      <c r="L6" s="8"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L6" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="M6" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="N6" s="8"/>
+    </row>
+    <row r="7" spans="1:14" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>52</v>
       </c>
       <c r="B7" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
+      <c r="C7" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>206</v>
+      </c>
+      <c r="J7" s="12">
+        <v>400</v>
+      </c>
       <c r="K7" s="8"/>
-      <c r="L7" s="8"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="5"/>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="5"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
-      <c r="K9" s="5"/>
-      <c r="L9" s="5"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="5"/>
-      <c r="L10" s="5"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="5"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
-      <c r="K11" s="5"/>
-      <c r="L11" s="5"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="5"/>
-      <c r="L12" s="5"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="5"/>
-      <c r="L13" s="5"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="5"/>
-      <c r="L14" s="5"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
-      <c r="K15" s="5"/>
-      <c r="L15" s="5"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="5"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
-      <c r="J16" s="5"/>
-      <c r="K16" s="5"/>
-      <c r="L16" s="5"/>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="5"/>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
-      <c r="I17" s="5"/>
-      <c r="J17" s="5"/>
-      <c r="K17" s="5"/>
-      <c r="L17" s="5"/>
+      <c r="L7" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="M7" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="N7" s="8"/>
+    </row>
+    <row r="8" spans="1:14" ht="77.25" x14ac:dyDescent="0.25">
+      <c r="A8" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="H8" s="19" t="s">
+        <v>207</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="J8" s="12">
+        <v>400</v>
+      </c>
+      <c r="K8" s="7"/>
+      <c r="L8" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="M8" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="N8" s="1"/>
+    </row>
+    <row r="9" spans="1:14" ht="102.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="H9" s="19" t="s">
+        <v>213</v>
+      </c>
+      <c r="I9" s="20" t="s">
+        <v>214</v>
+      </c>
+      <c r="J9" s="12">
+        <v>400</v>
+      </c>
+      <c r="K9" s="7"/>
+      <c r="L9" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="M9" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="N9" s="7"/>
+    </row>
+    <row r="10" spans="1:14" ht="90" x14ac:dyDescent="0.25">
+      <c r="A10" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="H10" s="19" t="s">
+        <v>215</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="J10" s="12">
+        <v>400</v>
+      </c>
+      <c r="K10" s="7"/>
+      <c r="L10" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="M10" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="N10" s="7"/>
+    </row>
+    <row r="11" spans="1:14" ht="90" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="H11" s="19" t="s">
+        <v>217</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="J11" s="12">
+        <v>400</v>
+      </c>
+      <c r="K11" s="7"/>
+      <c r="L11" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="M11" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="N11" s="7"/>
+    </row>
+    <row r="12" spans="1:14" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A12" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="I12" s="8"/>
+      <c r="J12" s="11">
+        <v>200</v>
+      </c>
+      <c r="K12" s="7"/>
+      <c r="L12" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="M12" s="7"/>
+      <c r="N12" s="7"/>
+    </row>
+    <row r="13" spans="1:14" ht="39" x14ac:dyDescent="0.25">
+      <c r="A13" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H13" s="19" t="s">
+        <v>221</v>
+      </c>
+      <c r="I13" s="8"/>
+      <c r="J13" s="11">
+        <v>200</v>
+      </c>
+      <c r="K13" s="7"/>
+      <c r="L13" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="M13" s="7"/>
+      <c r="N13" s="7"/>
+    </row>
+    <row r="14" spans="1:14" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A14" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="G14" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="I14" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="J14" s="11">
+        <v>200</v>
+      </c>
+      <c r="K14" s="7"/>
+      <c r="L14" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="M14" s="7"/>
+      <c r="N14" s="7"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -1212,4 +2037,1057 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{948644BA-B3E6-4AA8-BD5C-C2D4180A606F}">
+  <dimension ref="A1:N17"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="82.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="74.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="42.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="D1" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="E1" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="K1" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="L1" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="N1" s="22" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="15"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="15"/>
+      <c r="N2" s="15"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="F3" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="G3" s="17"/>
+      <c r="H3" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="I3" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="J3" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="K3" s="4"/>
+      <c r="L3" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M3" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="N3" s="15"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="H4" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="I4" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="J4" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="K4" s="4"/>
+      <c r="L4" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M4" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="N4" s="15"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="F5" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="H5" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="I5" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="J5" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="K5" s="4"/>
+      <c r="L5" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M5" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="N5" s="15"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="16" t="s">
+        <v>190</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="F6" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="G6" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="H6" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="I6" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="J6" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="K6" s="4"/>
+      <c r="L6" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M6" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="N6" s="15"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="H7" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="I7" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="J7" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="K7" s="4"/>
+      <c r="L7" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M7" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="N7" s="15"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="F8" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="G8" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="H8" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="I8" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="J8" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="K8" s="4"/>
+      <c r="L8" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M8" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="N8" s="15"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="F9" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="G9" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="H9" s="16" t="s">
+        <v>140</v>
+      </c>
+      <c r="I9" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="J9" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="K9" s="4"/>
+      <c r="L9" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="N9" s="15"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" s="16" t="s">
+        <v>194</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="E10" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="F10" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="G10" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="H10" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="I10" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="J10" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="K10" s="4"/>
+      <c r="L10" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="N10" s="15"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="16" t="s">
+        <v>195</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="E11" s="16" t="s">
+        <v>150</v>
+      </c>
+      <c r="F11" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="G11" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="H11" s="16" t="s">
+        <v>152</v>
+      </c>
+      <c r="I11" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="J11" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="K11" s="4"/>
+      <c r="L11" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="N11" s="15"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="E12" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="F12" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="G12" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="H12" s="16" t="s">
+        <v>157</v>
+      </c>
+      <c r="I12" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="J12" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="K12" s="4"/>
+      <c r="L12" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="N12" s="15"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="E13" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="F13" s="16" t="s">
+        <v>161</v>
+      </c>
+      <c r="G13" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="H13" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="I13" s="16" t="s">
+        <v>164</v>
+      </c>
+      <c r="J13" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="K13" s="4"/>
+      <c r="L13" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="N13" s="15"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="16" t="s">
+        <v>198</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>165</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="E14" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="F14" s="16" t="s">
+        <v>167</v>
+      </c>
+      <c r="G14" s="16" t="s">
+        <v>168</v>
+      </c>
+      <c r="H14" s="16" t="s">
+        <v>169</v>
+      </c>
+      <c r="I14" s="16" t="s">
+        <v>170</v>
+      </c>
+      <c r="J14" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="K14" s="4"/>
+      <c r="L14" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="N14" s="15"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" s="16" t="s">
+        <v>199</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="D15" s="16" t="s">
+        <v>172</v>
+      </c>
+      <c r="E15" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="F15" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="G15" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="H15" s="16" t="s">
+        <v>175</v>
+      </c>
+      <c r="I15" s="16" t="s">
+        <v>176</v>
+      </c>
+      <c r="J15" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="K15" s="4"/>
+      <c r="L15" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="N15" s="15"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" s="16" t="s">
+        <v>200</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>172</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="F16" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="G16" s="16" t="s">
+        <v>178</v>
+      </c>
+      <c r="H16" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="I16" s="16" t="s">
+        <v>180</v>
+      </c>
+      <c r="J16" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="K16" s="4"/>
+      <c r="L16" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="N16" s="15"/>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="B17" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>181</v>
+      </c>
+      <c r="D17" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="E17" s="16" t="s">
+        <v>182</v>
+      </c>
+      <c r="F17" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="G17" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="H17" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="I17" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="J17" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="K17" s="4"/>
+      <c r="L17" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="N17" s="15"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" location="'Test Scenario'!A1" display="&lt;&lt;&lt; Test Scenario" xr:uid="{F3FFE990-6EC2-4C32-8EE4-E86AE9A55CF9}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8D709DB-E34B-4388-9CCC-819E634EE3C8}">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" location="'Test Scenario'!A1" display="&lt;&lt;&lt; Test Scenario" xr:uid="{F82BEB34-2653-48DE-B8B1-67FEACABC45F}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE25DD96-2A29-4CE3-8867-93E1EDEDC333}">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" location="'Test Scenario'!A1" display="&lt;&lt;&lt; Test Scenario" xr:uid="{330969C2-9855-4D86-8345-09A0ADD60971}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF03AB7F-D9C4-4461-9846-104EBA468541}">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" location="'Test Scenario'!A1" display="&lt;&lt;&lt; Test Scenario" xr:uid="{D807802F-2F44-4232-A518-8ED8156C5023}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C98792E-6938-4A29-B2C3-0B829B829587}">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" location="'Test Scenario'!A1" display="&lt;&lt;&lt; Test Scenario" xr:uid="{CA70645D-6089-4EDB-A5F2-E66ED96CD5E0}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/ShopFlow API testCase.xlsx
+++ b/ShopFlow API testCase.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\QA Engineer\ShopFlow API\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{402D8CE8-952C-4F16-8B94-D2D193046430}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{684BAF32-71AA-4D20-9040-304035FC788E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13740" tabRatio="650" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13740" tabRatio="650" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Version History" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1162" uniqueCount="551">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1177" uniqueCount="553">
   <si>
     <t>Project Name</t>
   </si>
@@ -488,14 +488,8 @@
     <t>Create product with negative price</t>
   </si>
   <si>
-    <t>{"name":"Bad Item","price":-5,"categoryId":1,"stock":10}</t>
-  </si>
-  <si>
     <t>1. Send POST /api/products with negative price
 2. Verify behaviour</t>
-  </si>
-  <si>
-    <t>Validation error (or note: json-server permissive)</t>
   </si>
   <si>
     <t>400</t>
@@ -536,17 +530,6 @@
     <t>Product id=1 exists</t>
   </si>
   <si>
-    <t>productId = 1</t>
-  </si>
-  <si>
-    <t>1. Send GET /api/products/1
-2. Verify status 200
-3. Verify id=1 in response</t>
-  </si>
-  <si>
-    <t>Product details returned</t>
-  </si>
-  <si>
     <t>TC_Products_005</t>
   </si>
   <si>
@@ -563,9 +546,6 @@
 2. Verify status 404</t>
   </si>
   <si>
-    <t>Product not found</t>
-  </si>
-  <si>
     <t>404</t>
   </si>
   <si>
@@ -682,12 +662,6 @@
     <t>/api/products?_page=1&amp;_limit=3</t>
   </si>
   <si>
-    <t>Paginate products</t>
-  </si>
-  <si>
-    <t>More than 3 products exist</t>
-  </si>
-  <si>
     <t>_page=1&amp;_limit=3</t>
   </si>
   <si>
@@ -727,9 +701,6 @@
   </si>
   <si>
     <t>Update product price</t>
-  </si>
-  <si>
-    <t>{"price":129.99}</t>
   </si>
   <si>
     <t>1. Send PATCH /api/products/1
@@ -746,9 +717,6 @@
     <t>Update product stock to zero</t>
   </si>
   <si>
-    <t>{"stock":0}</t>
-  </si>
-  <si>
     <t>1. Send PATCH /api/products/1 with stock=0
 2. Verify status 200</t>
   </si>
@@ -1866,6 +1834,69 @@
   </si>
   <si>
     <t>Coupon deleted successfully</t>
+  </si>
+  <si>
+    <t>{
+    "name":"Rechargeable Lamp",
+    "categoryId": 2,
+    "price": 5000,
+    "stock":50,
+    "status": "active"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "name":"Rechargeable Lamp",
+    "categoryId": 2,
+    "price": -5000,
+    "stock":50,
+    "status": "active"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "error": "Price must be a positive number"
+}</t>
+  </si>
+  <si>
+    <t>Product id=11 exists</t>
+  </si>
+  <si>
+    <t>productId = 11</t>
+  </si>
+  <si>
+    <t>1. Send GET /api/products/1
+2. Verify status 200
+3. Verify id=11 in response</t>
+  </si>
+  <si>
+    <t>/api/products/11</t>
+  </si>
+  <si>
+    <t>{
+    "name": "Rechargeable Lamp",
+    "categoryId": 2,
+    "price": 5000,
+    "stock": 50,
+    "status": "active",
+    "id": 11
+}</t>
+  </si>
+  <si>
+    <t>MF13:G13</t>
+  </si>
+  <si>
+    <t>Update product stock to zero+G17</t>
+  </si>
+  <si>
+    <t>{
+    "price":129.99
+}</t>
+  </si>
+  <si>
+    <t>{
+     "stock":0
+}</t>
   </si>
 </sst>
 </file>
@@ -1974,7 +2005,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
@@ -2031,6 +2062,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3109,20 +3143,20 @@
   <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="30.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="82.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="74.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="42.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="38.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="35.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.85546875" style="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="31" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -3181,13 +3215,13 @@
       <c r="G2" s="5"/>
       <c r="H2" s="5"/>
       <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
+      <c r="J2" s="9"/>
       <c r="K2" s="5"/>
       <c r="L2" s="5"/>
       <c r="M2" s="5"/>
       <c r="N2" s="5"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A3" s="24" t="s">
         <v>121</v>
       </c>
@@ -3206,17 +3240,21 @@
       <c r="F3" s="24" t="s">
         <v>125</v>
       </c>
-      <c r="G3" s="8"/>
-      <c r="H3" s="24" t="s">
+      <c r="G3" s="8" t="s">
+        <v>541</v>
+      </c>
+      <c r="H3" s="8" t="s">
         <v>126</v>
       </c>
       <c r="I3" s="24" t="s">
         <v>127</v>
       </c>
-      <c r="J3" s="24" t="s">
+      <c r="J3" s="25" t="s">
         <v>128</v>
       </c>
-      <c r="K3" s="5"/>
+      <c r="K3" s="24" t="s">
+        <v>127</v>
+      </c>
       <c r="L3" s="24" t="s">
         <v>60</v>
       </c>
@@ -3225,7 +3263,7 @@
       </c>
       <c r="N3" s="5"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A4" s="24" t="s">
         <v>129</v>
       </c>
@@ -3244,19 +3282,21 @@
       <c r="F4" s="24" t="s">
         <v>125</v>
       </c>
-      <c r="G4" s="24" t="s">
+      <c r="G4" s="8" t="s">
+        <v>542</v>
+      </c>
+      <c r="H4" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="H4" s="24" t="s">
-        <v>132</v>
-      </c>
-      <c r="I4" s="24" t="s">
-        <v>133</v>
-      </c>
-      <c r="J4" s="24" t="s">
-        <v>134</v>
-      </c>
-      <c r="K4" s="5"/>
+      <c r="I4" s="8" t="s">
+        <v>543</v>
+      </c>
+      <c r="J4" s="25">
+        <v>400</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>543</v>
+      </c>
       <c r="L4" s="24" t="s">
         <v>60</v>
       </c>
@@ -3265,9 +3305,9 @@
       </c>
       <c r="N4" s="5"/>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A5" s="24" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B5" s="24" t="s">
         <v>122</v>
@@ -3279,24 +3319,26 @@
         <v>70</v>
       </c>
       <c r="E5" s="24" t="s">
+        <v>134</v>
+      </c>
+      <c r="F5" s="24" t="s">
+        <v>135</v>
+      </c>
+      <c r="G5" s="24" t="s">
         <v>136</v>
       </c>
-      <c r="F5" s="24" t="s">
+      <c r="H5" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="G5" s="24" t="s">
+      <c r="I5" s="24" t="s">
         <v>138</v>
       </c>
-      <c r="H5" s="24" t="s">
+      <c r="J5" s="25" t="s">
         <v>139</v>
       </c>
-      <c r="I5" s="24" t="s">
-        <v>140</v>
-      </c>
-      <c r="J5" s="24" t="s">
-        <v>141</v>
-      </c>
-      <c r="K5" s="5"/>
+      <c r="K5" s="24" t="s">
+        <v>138</v>
+      </c>
       <c r="L5" s="24" t="s">
         <v>60</v>
       </c>
@@ -3305,38 +3347,40 @@
       </c>
       <c r="N5" s="5"/>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="178.5" x14ac:dyDescent="0.25">
       <c r="A6" s="24" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B6" s="24" t="s">
         <v>122</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>143</v>
+        <v>547</v>
       </c>
       <c r="D6" s="24" t="s">
         <v>70</v>
       </c>
       <c r="E6" s="24" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F6" s="24" t="s">
-        <v>145</v>
+        <v>544</v>
       </c>
       <c r="G6" s="24" t="s">
-        <v>146</v>
-      </c>
-      <c r="H6" s="24" t="s">
-        <v>147</v>
-      </c>
-      <c r="I6" s="24" t="s">
-        <v>148</v>
-      </c>
-      <c r="J6" s="24" t="s">
-        <v>141</v>
-      </c>
-      <c r="K6" s="5"/>
+        <v>545</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>546</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>548</v>
+      </c>
+      <c r="J6" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>548</v>
+      </c>
       <c r="L6" s="24" t="s">
         <v>60</v>
       </c>
@@ -3345,38 +3389,40 @@
       </c>
       <c r="N6" s="5"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A7" s="24" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="B7" s="24" t="s">
         <v>122</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="D7" s="24" t="s">
         <v>70</v>
       </c>
       <c r="E7" s="24" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="F7" s="24" t="s">
         <v>125</v>
       </c>
       <c r="G7" s="24" t="s">
-        <v>152</v>
-      </c>
-      <c r="H7" s="24" t="s">
-        <v>153</v>
+        <v>147</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>148</v>
       </c>
       <c r="I7" s="24" t="s">
-        <v>154</v>
-      </c>
-      <c r="J7" s="24" t="s">
-        <v>155</v>
-      </c>
-      <c r="K7" s="5"/>
+        <v>81</v>
+      </c>
+      <c r="J7" s="25" t="s">
+        <v>149</v>
+      </c>
+      <c r="K7" s="24" t="s">
+        <v>81</v>
+      </c>
       <c r="L7" s="24" t="s">
         <v>60</v>
       </c>
@@ -3385,38 +3431,40 @@
       </c>
       <c r="N7" s="5"/>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A8" s="24" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="B8" s="24" t="s">
         <v>122</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="D8" s="24" t="s">
         <v>70</v>
       </c>
       <c r="E8" s="24" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="F8" s="24" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="G8" s="24" t="s">
-        <v>160</v>
-      </c>
-      <c r="H8" s="24" t="s">
-        <v>161</v>
+        <v>154</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>155</v>
       </c>
       <c r="I8" s="24" t="s">
-        <v>162</v>
-      </c>
-      <c r="J8" s="24" t="s">
-        <v>141</v>
-      </c>
-      <c r="K8" s="5"/>
+        <v>156</v>
+      </c>
+      <c r="J8" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="K8" s="24" t="s">
+        <v>156</v>
+      </c>
       <c r="L8" s="24" t="s">
         <v>60</v>
       </c>
@@ -3425,78 +3473,82 @@
       </c>
       <c r="N8" s="5"/>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A9" s="24" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="B9" s="24" t="s">
         <v>122</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="D9" s="24" t="s">
         <v>70</v>
       </c>
       <c r="E9" s="24" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="F9" s="24" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="G9" s="24" t="s">
-        <v>167</v>
-      </c>
-      <c r="H9" s="24" t="s">
-        <v>168</v>
+        <v>161</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>162</v>
       </c>
       <c r="I9" s="24" t="s">
-        <v>169</v>
-      </c>
-      <c r="J9" s="24" t="s">
-        <v>141</v>
-      </c>
-      <c r="K9" s="5"/>
+        <v>163</v>
+      </c>
+      <c r="J9" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="K9" s="24" t="s">
+        <v>163</v>
+      </c>
       <c r="L9" s="24" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="M9" s="24" t="s">
         <v>61</v>
       </c>
       <c r="N9" s="5"/>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A10" s="24" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="B10" s="24" t="s">
         <v>122</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="D10" s="24" t="s">
         <v>70</v>
       </c>
       <c r="E10" s="24" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="F10" s="24" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="G10" s="24" t="s">
-        <v>175</v>
-      </c>
-      <c r="H10" s="24" t="s">
-        <v>176</v>
+        <v>169</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>170</v>
       </c>
       <c r="I10" s="24" t="s">
-        <v>177</v>
-      </c>
-      <c r="J10" s="24" t="s">
-        <v>141</v>
-      </c>
-      <c r="K10" s="5"/>
+        <v>171</v>
+      </c>
+      <c r="J10" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="K10" s="24" t="s">
+        <v>171</v>
+      </c>
       <c r="L10" s="24" t="s">
         <v>60</v>
       </c>
@@ -3505,280 +3557,294 @@
       </c>
       <c r="N10" s="5"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A11" s="24" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="B11" s="24" t="s">
         <v>122</v>
       </c>
       <c r="C11" s="24" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="D11" s="24" t="s">
         <v>70</v>
       </c>
       <c r="E11" s="24" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="F11" s="24" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="G11" s="24" t="s">
-        <v>181</v>
-      </c>
-      <c r="H11" s="24" t="s">
-        <v>182</v>
+        <v>175</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>176</v>
       </c>
       <c r="I11" s="24" t="s">
-        <v>183</v>
-      </c>
-      <c r="J11" s="24" t="s">
-        <v>141</v>
-      </c>
-      <c r="K11" s="5"/>
+        <v>177</v>
+      </c>
+      <c r="J11" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="K11" s="24" t="s">
+        <v>177</v>
+      </c>
       <c r="L11" s="24" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="M11" s="24" t="s">
         <v>61</v>
       </c>
       <c r="N11" s="5"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A12" s="24" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="B12" s="24" t="s">
         <v>122</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="D12" s="24" t="s">
         <v>70</v>
       </c>
       <c r="E12" s="24" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="F12" s="24" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="G12" s="24" t="s">
-        <v>187</v>
-      </c>
-      <c r="H12" s="24" t="s">
-        <v>188</v>
+        <v>181</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>182</v>
       </c>
       <c r="I12" s="24" t="s">
-        <v>189</v>
-      </c>
-      <c r="J12" s="24" t="s">
-        <v>141</v>
-      </c>
-      <c r="K12" s="5"/>
+        <v>183</v>
+      </c>
+      <c r="J12" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="K12" s="24" t="s">
+        <v>183</v>
+      </c>
       <c r="L12" s="24" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="M12" s="24" t="s">
         <v>61</v>
       </c>
       <c r="N12" s="5"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A13" s="24" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="B13" s="24" t="s">
         <v>122</v>
       </c>
       <c r="C13" s="24" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="D13" s="24" t="s">
         <v>70</v>
       </c>
       <c r="E13" s="24" t="s">
-        <v>192</v>
+        <v>550</v>
       </c>
       <c r="F13" s="24" t="s">
-        <v>193</v>
+        <v>549</v>
       </c>
       <c r="G13" s="24" t="s">
-        <v>194</v>
-      </c>
-      <c r="H13" s="24" t="s">
-        <v>195</v>
+        <v>186</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>187</v>
       </c>
       <c r="I13" s="24" t="s">
-        <v>196</v>
-      </c>
-      <c r="J13" s="24" t="s">
-        <v>141</v>
-      </c>
-      <c r="K13" s="5"/>
+        <v>188</v>
+      </c>
+      <c r="J13" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="K13" s="24" t="s">
+        <v>188</v>
+      </c>
       <c r="L13" s="24" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="M13" s="24" t="s">
         <v>61</v>
       </c>
       <c r="N13" s="5"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A14" s="24" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="B14" s="24" t="s">
         <v>122</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="D14" s="24" t="s">
         <v>70</v>
       </c>
       <c r="E14" s="24" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="F14" s="24" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="G14" s="24" t="s">
-        <v>201</v>
-      </c>
-      <c r="H14" s="24" t="s">
-        <v>202</v>
+        <v>193</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>194</v>
       </c>
       <c r="I14" s="24" t="s">
-        <v>203</v>
-      </c>
-      <c r="J14" s="24" t="s">
-        <v>141</v>
-      </c>
-      <c r="K14" s="5"/>
+        <v>195</v>
+      </c>
+      <c r="J14" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="K14" s="24" t="s">
+        <v>195</v>
+      </c>
       <c r="L14" s="24" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="M14" s="24" t="s">
         <v>61</v>
       </c>
       <c r="N14" s="5"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A15" s="24" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="B15" s="24" t="s">
         <v>122</v>
       </c>
       <c r="C15" s="24" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D15" s="24" t="s">
         <v>113</v>
       </c>
       <c r="E15" s="24" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="F15" s="24" t="s">
-        <v>145</v>
-      </c>
-      <c r="G15" s="24" t="s">
-        <v>207</v>
-      </c>
-      <c r="H15" s="24" t="s">
-        <v>208</v>
+        <v>143</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>551</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>199</v>
       </c>
       <c r="I15" s="24" t="s">
-        <v>209</v>
-      </c>
-      <c r="J15" s="24" t="s">
-        <v>141</v>
-      </c>
-      <c r="K15" s="5"/>
+        <v>200</v>
+      </c>
+      <c r="J15" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="K15" s="24" t="s">
+        <v>200</v>
+      </c>
       <c r="L15" s="24" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="M15" s="24" t="s">
         <v>61</v>
       </c>
       <c r="N15" s="5"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A16" s="24" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="B16" s="24" t="s">
         <v>122</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D16" s="24" t="s">
         <v>113</v>
       </c>
       <c r="E16" s="24" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="F16" s="24" t="s">
-        <v>145</v>
-      </c>
-      <c r="G16" s="24" t="s">
-        <v>212</v>
-      </c>
-      <c r="H16" s="24" t="s">
-        <v>213</v>
+        <v>143</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>552</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>203</v>
       </c>
       <c r="I16" s="24" t="s">
-        <v>214</v>
-      </c>
-      <c r="J16" s="24" t="s">
-        <v>141</v>
-      </c>
-      <c r="K16" s="5"/>
+        <v>204</v>
+      </c>
+      <c r="J16" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="K16" s="24" t="s">
+        <v>204</v>
+      </c>
       <c r="L16" s="24" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="M16" s="24" t="s">
         <v>61</v>
       </c>
       <c r="N16" s="5"/>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A17" s="24" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="B17" s="24" t="s">
         <v>122</v>
       </c>
       <c r="C17" s="24" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="D17" s="24" t="s">
         <v>118</v>
       </c>
       <c r="E17" s="24" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="F17" s="24" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="G17" s="24" t="s">
-        <v>219</v>
-      </c>
-      <c r="H17" s="24" t="s">
-        <v>220</v>
+        <v>209</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>210</v>
       </c>
       <c r="I17" s="24" t="s">
-        <v>221</v>
-      </c>
-      <c r="J17" s="24" t="s">
-        <v>141</v>
-      </c>
-      <c r="K17" s="5"/>
+        <v>211</v>
+      </c>
+      <c r="J17" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="K17" s="24" t="s">
+        <v>211</v>
+      </c>
       <c r="L17" s="24" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="M17" s="24" t="s">
         <v>61</v>
@@ -3878,31 +3944,31 @@
     </row>
     <row r="3" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="D3" s="12" t="s">
         <v>54</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="H3" s="12" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="I3" s="12" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="J3" s="23" t="s">
         <v>128</v>
@@ -3918,34 +3984,34 @@
     </row>
     <row r="4" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="D4" s="12" t="s">
         <v>54</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="F4" s="12" t="s">
         <v>125</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="J4" s="23" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="K4" s="12"/>
       <c r="L4" s="12" t="s">
@@ -3958,34 +4024,34 @@
     </row>
     <row r="5" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="D5" s="12" t="s">
         <v>54</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="F5" s="12" t="s">
         <v>125</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="I5" s="12" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="J5" s="23" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="K5" s="12"/>
       <c r="L5" s="12" t="s">
@@ -3998,34 +4064,34 @@
     </row>
     <row r="6" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="D6" s="12" t="s">
         <v>54</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="F6" s="12" t="s">
         <v>125</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="I6" s="12" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="J6" s="23" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="K6" s="12"/>
       <c r="L6" s="12" t="s">
@@ -4038,34 +4104,34 @@
     </row>
     <row r="7" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="D7" s="12" t="s">
         <v>54</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="F7" s="12" t="s">
         <v>125</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="J7" s="23" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="K7" s="12"/>
       <c r="L7" s="12" t="s">
@@ -4078,38 +4144,38 @@
     </row>
     <row r="8" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="D8" s="12" t="s">
         <v>54</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="F8" s="12" t="s">
         <v>125</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="J8" s="23" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="K8" s="12"/>
       <c r="L8" s="12" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="M8" s="12" t="s">
         <v>67</v>
@@ -4118,38 +4184,38 @@
     </row>
     <row r="9" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="D9" s="12" t="s">
         <v>54</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="F9" s="12" t="s">
         <v>125</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="I9" s="12" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="J9" s="23" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="K9" s="12"/>
       <c r="L9" s="12" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="M9" s="12" t="s">
         <v>67</v>
@@ -4158,34 +4224,34 @@
     </row>
     <row r="10" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="D10" s="12" t="s">
         <v>70</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="J10" s="23" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="K10" s="12"/>
       <c r="L10" s="12" t="s">
@@ -4198,34 +4264,34 @@
     </row>
     <row r="11" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="D11" s="12" t="s">
         <v>70</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="H11" s="12" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="I11" s="12" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="J11" s="23" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="K11" s="12"/>
       <c r="L11" s="12" t="s">
@@ -4238,34 +4304,34 @@
     </row>
     <row r="12" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="D12" s="12" t="s">
         <v>70</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="F12" s="12" t="s">
         <v>125</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="H12" s="12" t="s">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="I12" s="12" t="s">
         <v>81</v>
       </c>
       <c r="J12" s="23" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="K12" s="12"/>
       <c r="L12" s="12" t="s">
@@ -4278,34 +4344,34 @@
     </row>
     <row r="13" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="D13" s="12" t="s">
         <v>70</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="H13" s="12" t="s">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="I13" s="12" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="J13" s="23" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="K13" s="12"/>
       <c r="L13" s="12" t="s">
@@ -4318,34 +4384,34 @@
     </row>
     <row r="14" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="D14" s="12" t="s">
         <v>70</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="H14" s="12" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="I14" s="12" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="J14" s="23" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="K14" s="12"/>
       <c r="L14" s="12" t="s">
@@ -4358,34 +4424,34 @@
     </row>
     <row r="15" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="D15" s="12" t="s">
         <v>113</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="H15" s="12" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="I15" s="12" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="J15" s="23" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="K15" s="12"/>
       <c r="L15" s="12" t="s">
@@ -4398,34 +4464,34 @@
     </row>
     <row r="16" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="D16" s="12" t="s">
         <v>70</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="H16" s="12" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="I16" s="12" t="s">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="J16" s="23" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="K16" s="12"/>
       <c r="L16" s="12" t="s">
@@ -4438,38 +4504,38 @@
     </row>
     <row r="17" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="D17" s="12" t="s">
         <v>118</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="F17" s="12" t="s">
         <v>125</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="H17" s="12" t="s">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="I17" s="12" t="s">
         <v>81</v>
       </c>
       <c r="J17" s="23" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="K17" s="12"/>
       <c r="L17" s="12" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="M17" s="12" t="s">
         <v>67</v>
@@ -4566,31 +4632,31 @@
     </row>
     <row r="3" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>54</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="J3" s="10" t="s">
         <v>128</v>
@@ -4606,34 +4672,34 @@
     </row>
     <row r="4" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="D4" s="10" t="s">
         <v>54</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="F4" s="8" t="s">
         <v>125</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="K4" s="8"/>
       <c r="L4" s="8" t="s">
@@ -4646,34 +4712,34 @@
     </row>
     <row r="5" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="D5" s="10" t="s">
         <v>54</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>125</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="J5" s="10" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="K5" s="8"/>
       <c r="L5" s="8" t="s">
@@ -4686,34 +4752,34 @@
     </row>
     <row r="6" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="D6" s="10" t="s">
         <v>54</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>125</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="K6" s="8"/>
       <c r="L6" s="8" t="s">
@@ -4726,34 +4792,34 @@
     </row>
     <row r="7" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="D7" s="10" t="s">
         <v>54</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>125</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="K7" s="8"/>
       <c r="L7" s="8" t="s">
@@ -4766,34 +4832,34 @@
     </row>
     <row r="8" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="D8" s="10" t="s">
         <v>54</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>125</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="K8" s="8"/>
       <c r="L8" s="8" t="s">
@@ -4806,34 +4872,34 @@
     </row>
     <row r="9" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="D9" s="10" t="s">
         <v>54</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>125</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="J9" s="10" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="K9" s="8"/>
       <c r="L9" s="8" t="s">
@@ -4846,34 +4912,34 @@
     </row>
     <row r="10" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="D10" s="10" t="s">
         <v>54</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="F10" s="8" t="s">
         <v>125</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="K10" s="8"/>
       <c r="L10" s="8" t="s">
@@ -4886,34 +4952,34 @@
     </row>
     <row r="11" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="D11" s="10" t="s">
         <v>70</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="K11" s="8"/>
       <c r="L11" s="8" t="s">
@@ -4926,34 +4992,34 @@
     </row>
     <row r="12" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>70</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>353</v>
+        <v>343</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="K12" s="8"/>
       <c r="L12" s="8" t="s">
@@ -4966,34 +5032,34 @@
     </row>
     <row r="13" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="D13" s="10" t="s">
         <v>70</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>125</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="I13" s="8" t="s">
         <v>81</v>
       </c>
       <c r="J13" s="10" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="K13" s="8"/>
       <c r="L13" s="8" t="s">
@@ -5006,34 +5072,34 @@
     </row>
     <row r="14" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>363</v>
+        <v>353</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="D14" s="10" t="s">
         <v>70</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="J14" s="10" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="K14" s="8"/>
       <c r="L14" s="8" t="s">
@@ -5046,38 +5112,38 @@
     </row>
     <row r="15" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="D15" s="10" t="s">
         <v>70</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="K15" s="8"/>
       <c r="L15" s="8" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="M15" s="8" t="s">
         <v>61</v>
@@ -5086,38 +5152,38 @@
     </row>
     <row r="16" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="D16" s="10" t="s">
         <v>113</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="J16" s="10" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="K16" s="8"/>
       <c r="L16" s="8" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="M16" s="8" t="s">
         <v>61</v>
@@ -5126,38 +5192,38 @@
     </row>
     <row r="17" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="D17" s="10" t="s">
         <v>118</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="J17" s="10" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="K17" s="8"/>
       <c r="L17" s="8" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="M17" s="8" t="s">
         <v>61</v>
@@ -5254,31 +5320,31 @@
     </row>
     <row r="3" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>54</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="F3" s="8" t="s">
         <v>72</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>393</v>
+        <v>383</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="J3" s="8" t="s">
         <v>128</v>
@@ -5294,34 +5360,34 @@
     </row>
     <row r="4" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>54</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>397</v>
+        <v>387</v>
       </c>
       <c r="F4" s="8" t="s">
         <v>125</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="K4" s="8"/>
       <c r="L4" s="8" t="s">
@@ -5334,34 +5400,34 @@
     </row>
     <row r="5" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>54</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>401</v>
+        <v>391</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>125</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>402</v>
+        <v>392</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>403</v>
+        <v>393</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="K5" s="8"/>
       <c r="L5" s="8" t="s">
@@ -5374,34 +5440,34 @@
     </row>
     <row r="6" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>404</v>
+        <v>394</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>54</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>405</v>
+        <v>395</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>125</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>406</v>
+        <v>396</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>408</v>
+        <v>398</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="K6" s="8"/>
       <c r="L6" s="8" t="s">
@@ -5414,34 +5480,34 @@
     </row>
     <row r="7" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>409</v>
+        <v>399</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>54</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>125</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>411</v>
+        <v>401</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>412</v>
+        <v>402</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>413</v>
+        <v>403</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="K7" s="8"/>
       <c r="L7" s="8" t="s">
@@ -5454,34 +5520,34 @@
     </row>
     <row r="8" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>414</v>
+        <v>404</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>70</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>415</v>
+        <v>405</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>417</v>
+        <v>407</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="K8" s="8"/>
       <c r="L8" s="8" t="s">
@@ -5494,34 +5560,34 @@
     </row>
     <row r="9" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>419</v>
+        <v>409</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>70</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>421</v>
+        <v>411</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>422</v>
+        <v>412</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>423</v>
+        <v>413</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>424</v>
+        <v>414</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>425</v>
+        <v>415</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="K9" s="8"/>
       <c r="L9" s="8" t="s">
@@ -5534,34 +5600,34 @@
     </row>
     <row r="10" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>426</v>
+        <v>416</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>427</v>
+        <v>417</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>70</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>428</v>
+        <v>418</v>
       </c>
       <c r="F10" s="8" t="s">
         <v>125</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="I10" s="8" t="s">
         <v>81</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="K10" s="8"/>
       <c r="L10" s="8" t="s">
@@ -5574,34 +5640,34 @@
     </row>
     <row r="11" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>431</v>
+        <v>421</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>432</v>
+        <v>422</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>70</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>433</v>
+        <v>423</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>434</v>
+        <v>424</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>435</v>
+        <v>425</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="K11" s="8"/>
       <c r="L11" s="8" t="s">
@@ -5614,34 +5680,34 @@
     </row>
     <row r="12" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>113</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>438</v>
+        <v>428</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>422</v>
+        <v>412</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>441</v>
+        <v>431</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="K12" s="8"/>
       <c r="L12" s="8" t="s">
@@ -5654,38 +5720,38 @@
     </row>
     <row r="13" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>442</v>
+        <v>432</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>113</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>443</v>
+        <v>433</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>422</v>
+        <v>412</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>444</v>
+        <v>434</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>445</v>
+        <v>435</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>446</v>
+        <v>436</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="K13" s="8"/>
       <c r="L13" s="8" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="M13" s="8" t="s">
         <v>61</v>
@@ -5694,38 +5760,38 @@
     </row>
     <row r="14" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>447</v>
+        <v>437</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="D14" s="8" t="s">
         <v>113</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>448</v>
+        <v>438</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>422</v>
+        <v>412</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>449</v>
+        <v>439</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>451</v>
+        <v>441</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="K14" s="8"/>
       <c r="L14" s="8" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="M14" s="8" t="s">
         <v>61</v>
@@ -5734,38 +5800,38 @@
     </row>
     <row r="15" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>453</v>
+        <v>443</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>454</v>
+        <v>444</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>422</v>
+        <v>412</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>456</v>
+        <v>446</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>457</v>
+        <v>447</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="K15" s="8"/>
       <c r="L15" s="8" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="M15" s="8" t="s">
         <v>61</v>
@@ -5774,38 +5840,38 @@
     </row>
     <row r="16" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>458</v>
+        <v>448</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="D16" s="8" t="s">
         <v>118</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>459</v>
+        <v>449</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>422</v>
+        <v>412</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>424</v>
+        <v>414</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>461</v>
+        <v>451</v>
       </c>
       <c r="J16" s="8" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="K16" s="8"/>
       <c r="L16" s="8" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="M16" s="8" t="s">
         <v>61</v>
@@ -5814,38 +5880,38 @@
     </row>
     <row r="17" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>462</v>
+        <v>452</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>427</v>
+        <v>417</v>
       </c>
       <c r="D17" s="8" t="s">
         <v>118</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>463</v>
+        <v>453</v>
       </c>
       <c r="F17" s="8" t="s">
         <v>125</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="I17" s="8" t="s">
         <v>81</v>
       </c>
       <c r="J17" s="8" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="K17" s="8"/>
       <c r="L17" s="8" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="M17" s="8" t="s">
         <v>67</v>
@@ -5942,31 +6008,31 @@
     </row>
     <row r="3" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>465</v>
+        <v>455</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>466</v>
+        <v>456</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>54</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>468</v>
+        <v>458</v>
       </c>
       <c r="F3" s="8" t="s">
         <v>125</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>469</v>
+        <v>459</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>470</v>
+        <v>460</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>471</v>
+        <v>461</v>
       </c>
       <c r="J3" s="8" t="s">
         <v>128</v>
@@ -5982,34 +6048,34 @@
     </row>
     <row r="4" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>472</v>
+        <v>462</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>466</v>
+        <v>456</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>54</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>473</v>
+        <v>463</v>
       </c>
       <c r="F4" s="8" t="s">
         <v>125</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>474</v>
+        <v>464</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>476</v>
+        <v>466</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="K4" s="8"/>
       <c r="L4" s="8" t="s">
@@ -6022,34 +6088,34 @@
     </row>
     <row r="5" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>477</v>
+        <v>467</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>466</v>
+        <v>456</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>54</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>478</v>
+        <v>468</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>125</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>480</v>
+        <v>470</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>481</v>
+        <v>471</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="K5" s="8"/>
       <c r="L5" s="8" t="s">
@@ -6062,34 +6128,34 @@
     </row>
     <row r="6" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>482</v>
+        <v>472</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>466</v>
+        <v>456</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>54</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>125</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>484</v>
+        <v>474</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>485</v>
+        <v>475</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="K6" s="8"/>
       <c r="L6" s="8" t="s">
@@ -6102,34 +6168,34 @@
     </row>
     <row r="7" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>487</v>
+        <v>477</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>466</v>
+        <v>456</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>54</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>488</v>
+        <v>478</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>125</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>489</v>
+        <v>479</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>490</v>
+        <v>480</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>491</v>
+        <v>481</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="K7" s="8"/>
       <c r="L7" s="8" t="s">
@@ -6142,34 +6208,34 @@
     </row>
     <row r="8" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>492</v>
+        <v>482</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>466</v>
+        <v>456</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>54</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>493</v>
+        <v>483</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>125</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>494</v>
+        <v>484</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>495</v>
+        <v>485</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>496</v>
+        <v>486</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="K8" s="8"/>
       <c r="L8" s="8" t="s">
@@ -6182,34 +6248,34 @@
     </row>
     <row r="9" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>497</v>
+        <v>487</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>466</v>
+        <v>456</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>54</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>498</v>
+        <v>488</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>125</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>499</v>
+        <v>489</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>500</v>
+        <v>490</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>501</v>
+        <v>491</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="K9" s="8"/>
       <c r="L9" s="8" t="s">
@@ -6222,34 +6288,34 @@
     </row>
     <row r="10" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>466</v>
+        <v>456</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>54</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>503</v>
+        <v>493</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>504</v>
+        <v>494</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>505</v>
+        <v>495</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>506</v>
+        <v>496</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>507</v>
+        <v>497</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="K10" s="8"/>
       <c r="L10" s="8" t="s">
@@ -6262,34 +6328,34 @@
     </row>
     <row r="11" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>508</v>
+        <v>498</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>466</v>
+        <v>456</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>70</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>509</v>
+        <v>499</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>511</v>
+        <v>501</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>512</v>
+        <v>502</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="K11" s="8"/>
       <c r="L11" s="8" t="s">
@@ -6302,34 +6368,34 @@
     </row>
     <row r="12" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>513</v>
+        <v>503</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>466</v>
+        <v>456</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>514</v>
+        <v>504</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>70</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>516</v>
+        <v>506</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>517</v>
+        <v>507</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>518</v>
+        <v>508</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>519</v>
+        <v>509</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="K12" s="8"/>
       <c r="L12" s="8" t="s">
@@ -6342,34 +6408,34 @@
     </row>
     <row r="13" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>520</v>
+        <v>510</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>466</v>
+        <v>456</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>521</v>
+        <v>511</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>70</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>522</v>
+        <v>512</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>125</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>523</v>
+        <v>513</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>524</v>
+        <v>514</v>
       </c>
       <c r="I13" s="8" t="s">
         <v>81</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="K13" s="8"/>
       <c r="L13" s="8" t="s">
@@ -6382,34 +6448,34 @@
     </row>
     <row r="14" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>525</v>
+        <v>515</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>466</v>
+        <v>456</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>526</v>
+        <v>516</v>
       </c>
       <c r="D14" s="8" t="s">
         <v>70</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>527</v>
+        <v>517</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>528</v>
+        <v>518</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>529</v>
+        <v>519</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>530</v>
+        <v>520</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>531</v>
+        <v>521</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="K14" s="8"/>
       <c r="L14" s="8" t="s">
@@ -6422,38 +6488,38 @@
     </row>
     <row r="15" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>532</v>
+        <v>522</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>466</v>
+        <v>456</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>533</v>
+        <v>523</v>
       </c>
       <c r="D15" s="8" t="s">
         <v>70</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>534</v>
+        <v>524</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>535</v>
+        <v>525</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>536</v>
+        <v>526</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>537</v>
+        <v>527</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>538</v>
+        <v>528</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="K15" s="8"/>
       <c r="L15" s="8" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="M15" s="8" t="s">
         <v>61</v>
@@ -6462,34 +6528,34 @@
     </row>
     <row r="16" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>539</v>
+        <v>529</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>466</v>
+        <v>456</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>514</v>
+        <v>504</v>
       </c>
       <c r="D16" s="8" t="s">
         <v>113</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>540</v>
+        <v>530</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>516</v>
+        <v>506</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>541</v>
+        <v>531</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>542</v>
+        <v>532</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>543</v>
+        <v>533</v>
       </c>
       <c r="J16" s="8" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="K16" s="8"/>
       <c r="L16" s="8" t="s">
@@ -6502,38 +6568,38 @@
     </row>
     <row r="17" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>544</v>
+        <v>534</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>466</v>
+        <v>456</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>545</v>
+        <v>535</v>
       </c>
       <c r="D17" s="8" t="s">
         <v>118</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>546</v>
+        <v>536</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>547</v>
+        <v>537</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>548</v>
+        <v>538</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>549</v>
+        <v>539</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>550</v>
+        <v>540</v>
       </c>
       <c r="J17" s="8" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="K17" s="8"/>
       <c r="L17" s="8" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="M17" s="8" t="s">
         <v>61</v>

--- a/ShopFlow API testCase.xlsx
+++ b/ShopFlow API testCase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\QA Engineer\ShopFlow API\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{684BAF32-71AA-4D20-9040-304035FC788E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB3EDE5D-AC21-4ECA-9C63-08FFC86987C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13740" tabRatio="650" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13740" tabRatio="650" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Version History" sheetId="1" r:id="rId1"/>
@@ -767,9 +767,6 @@
 3. Verify id in response</t>
   </si>
   <si>
-    <t>{"userId":2,"items":[{"productId":2,"quantity":1,"unitPrice":599.99}],"paymentMethod":"bank_transfer","status":"pending","subtotal":599.99,"tax":48,"shippingFee":0,"total":647.99}</t>
-  </si>
-  <si>
     <t>Order created successfully</t>
   </si>
   <si>
@@ -784,9 +781,6 @@
 3. Verify error message</t>
   </si>
   <si>
-    <t>{"items":[{"productId":1,"quantity":1}],"paymentMethod":"card"}</t>
-  </si>
-  <si>
     <t>{"error":"userId is required"}</t>
   </si>
   <si>
@@ -801,9 +795,6 @@
 3. Verify error message</t>
   </si>
   <si>
-    <t>{"userId":9999,"items":[{"productId":1,"quantity":1}],"paymentMethod":"card"}</t>
-  </si>
-  <si>
     <t>{"error":"User not found"}</t>
   </si>
   <si>
@@ -818,9 +809,6 @@
 3. Verify error message</t>
   </si>
   <si>
-    <t>{"userId":1,"items":[],"paymentMethod":"card"}</t>
-  </si>
-  <si>
     <t>{"error":"Order must contain at least one item"}</t>
   </si>
   <si>
@@ -835,9 +823,6 @@
 3. Verify error message</t>
   </si>
   <si>
-    <t>{"userId":1,"paymentMethod":"card"}</t>
-  </si>
-  <si>
     <t>{"error":"Items are required"}</t>
   </si>
   <si>
@@ -851,9 +836,6 @@
 2. Verify status 400</t>
   </si>
   <si>
-    <t>{"userId":1,"items":[{"productId":1,"quantity":1}],"paymentMethod":"crypto"}</t>
-  </si>
-  <si>
     <t>{"error":"Invalid payment method"}</t>
   </si>
   <si>
@@ -865,12 +847,6 @@
   <si>
     <t>1. Send POST /api/orders with status=unknown
 2. Verify status 400</t>
-  </si>
-  <si>
-    <t>{"userId":1,"items":[{"productId":1,"quantity":1}],"paymentMethod":"card","status":"unknown"}</t>
-  </si>
-  <si>
-    <t>{"error":"Invalid order status"}</t>
   </si>
   <si>
     <t>TC_Orders_008</t>
@@ -988,9 +964,6 @@
     <t>1. Send PATCH /api/orders/2
 2. Verify status 200
 3. Verify status=shipped</t>
-  </si>
-  <si>
-    <t>{"status":"shipped"}</t>
   </si>
   <si>
     <t>Order status updated to shipped</t>
@@ -1896,6 +1869,87 @@
   <si>
     <t>{
      "stock":0
+}</t>
+  </si>
+  <si>
+    <t>{
+  "userId": 1,
+  "items": [
+    {
+      "productId": 1,
+      "quantity": 1,
+      "unitPrice": 149.99
+    }
+  ]
+}</t>
+  </si>
+  <si>
+    <t>{
+  "items": [
+    {
+      "productId": 1,
+      "quantity": 1,
+      "unitPrice": 149.99
+    }
+  ]
+}</t>
+  </si>
+  <si>
+    <t>{
+    "error": "Invalid order status"
+}</t>
+  </si>
+  <si>
+    <t>{
+  "userId": 1,
+  "items": []
+}</t>
+  </si>
+  <si>
+    <t>{
+  "userId": 999,
+  "items": [
+    {
+      "productId": 1,
+      "quantity": 1,
+      "unitPrice": 149.99
+    }
+  ]
+}</t>
+  </si>
+  <si>
+    <t>{
+  "userId": 1
+}</t>
+  </si>
+  <si>
+    <t>{
+    "userId":1,
+    "items":[
+        {
+            "productId":1,
+            "quantity":1
+        }
+        ],
+        "paymentMethod":"crypto"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "userId":1,
+    "items":[
+        {
+            "productId":1,
+            "quantity":1
+            }
+        ],
+            "paymentMethod":"card",
+            "status":"unknown"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "status":"shipped"
 }</t>
   </si>
 </sst>
@@ -3241,7 +3295,7 @@
         <v>125</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>541</v>
+        <v>532</v>
       </c>
       <c r="H3" s="8" t="s">
         <v>126</v>
@@ -3283,19 +3337,19 @@
         <v>125</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>542</v>
+        <v>533</v>
       </c>
       <c r="H4" s="8" t="s">
         <v>131</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>543</v>
+        <v>534</v>
       </c>
       <c r="J4" s="25">
         <v>400</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>543</v>
+        <v>534</v>
       </c>
       <c r="L4" s="24" t="s">
         <v>60</v>
@@ -3355,7 +3409,7 @@
         <v>122</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>547</v>
+        <v>538</v>
       </c>
       <c r="D6" s="24" t="s">
         <v>70</v>
@@ -3364,22 +3418,22 @@
         <v>142</v>
       </c>
       <c r="F6" s="24" t="s">
-        <v>544</v>
+        <v>535</v>
       </c>
       <c r="G6" s="24" t="s">
-        <v>545</v>
+        <v>536</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>546</v>
+        <v>537</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>548</v>
+        <v>539</v>
       </c>
       <c r="J6" s="25" t="s">
         <v>139</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>548</v>
+        <v>539</v>
       </c>
       <c r="L6" s="24" t="s">
         <v>60</v>
@@ -3655,10 +3709,10 @@
         <v>70</v>
       </c>
       <c r="E13" s="24" t="s">
-        <v>550</v>
+        <v>541</v>
       </c>
       <c r="F13" s="24" t="s">
-        <v>549</v>
+        <v>540</v>
       </c>
       <c r="G13" s="24" t="s">
         <v>186</v>
@@ -3745,7 +3799,7 @@
         <v>143</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>551</v>
+        <v>542</v>
       </c>
       <c r="H15" s="8" t="s">
         <v>199</v>
@@ -3787,7 +3841,7 @@
         <v>143</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>552</v>
+        <v>543</v>
       </c>
       <c r="H16" s="8" t="s">
         <v>203</v>
@@ -3866,8 +3920,8 @@
   <cols>
     <col min="1" max="1" width="16.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.42578125" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" style="11" customWidth="1"/>
     <col min="5" max="5" width="33" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="38.7109375" bestFit="1" customWidth="1"/>
@@ -3942,7 +3996,7 @@
       <c r="M2" s="5"/>
       <c r="N2" s="5"/>
     </row>
-    <row r="3" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" ht="150" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
         <v>212</v>
       </c>
@@ -3952,7 +4006,7 @@
       <c r="C3" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="23" t="s">
         <v>54</v>
       </c>
       <c r="E3" s="12" t="s">
@@ -3965,10 +4019,10 @@
         <v>217</v>
       </c>
       <c r="H3" s="12" t="s">
+        <v>544</v>
+      </c>
+      <c r="I3" s="12" t="s">
         <v>218</v>
-      </c>
-      <c r="I3" s="12" t="s">
-        <v>219</v>
       </c>
       <c r="J3" s="23" t="s">
         <v>128</v>
@@ -3982,9 +4036,9 @@
       </c>
       <c r="N3" s="12"/>
     </row>
-    <row r="4" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" ht="135" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B4" s="12" t="s">
         <v>213</v>
@@ -3992,23 +4046,23 @@
       <c r="C4" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="23" t="s">
         <v>54</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F4" s="12" t="s">
         <v>125</v>
       </c>
       <c r="G4" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>545</v>
+      </c>
+      <c r="I4" s="12" t="s">
         <v>222</v>
-      </c>
-      <c r="H4" s="12" t="s">
-        <v>223</v>
-      </c>
-      <c r="I4" s="12" t="s">
-        <v>224</v>
       </c>
       <c r="J4" s="23" t="s">
         <v>132</v>
@@ -4024,7 +4078,7 @@
     </row>
     <row r="5" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B5" s="12" t="s">
         <v>213</v>
@@ -4032,23 +4086,23 @@
       <c r="C5" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="23" t="s">
         <v>54</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="F5" s="12" t="s">
         <v>125</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>228</v>
+        <v>548</v>
       </c>
       <c r="I5" s="12" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="J5" s="23" t="s">
         <v>132</v>
@@ -4064,7 +4118,7 @@
     </row>
     <row r="6" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>213</v>
@@ -4072,23 +4126,23 @@
       <c r="C6" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="23" t="s">
         <v>54</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="F6" s="12" t="s">
         <v>125</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>233</v>
+        <v>547</v>
       </c>
       <c r="I6" s="12" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="J6" s="23" t="s">
         <v>132</v>
@@ -4104,7 +4158,7 @@
     </row>
     <row r="7" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="B7" s="12" t="s">
         <v>213</v>
@@ -4112,23 +4166,23 @@
       <c r="C7" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="23" t="s">
         <v>54</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="F7" s="12" t="s">
         <v>125</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>238</v>
+        <v>549</v>
       </c>
       <c r="I7" s="12" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="J7" s="23" t="s">
         <v>132</v>
@@ -4144,7 +4198,7 @@
     </row>
     <row r="8" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="B8" s="12" t="s">
         <v>213</v>
@@ -4152,23 +4206,23 @@
       <c r="C8" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="23" t="s">
         <v>54</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="F8" s="12" t="s">
         <v>125</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>243</v>
+        <v>550</v>
       </c>
       <c r="I8" s="12" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="J8" s="23" t="s">
         <v>132</v>
@@ -4184,7 +4238,7 @@
     </row>
     <row r="9" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="B9" s="12" t="s">
         <v>213</v>
@@ -4192,23 +4246,23 @@
       <c r="C9" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="23" t="s">
         <v>54</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="F9" s="12" t="s">
         <v>125</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>248</v>
+        <v>551</v>
       </c>
       <c r="I9" s="12" t="s">
-        <v>249</v>
+        <v>546</v>
       </c>
       <c r="J9" s="23" t="s">
         <v>132</v>
@@ -4224,7 +4278,7 @@
     </row>
     <row r="10" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="B10" s="12" t="s">
         <v>213</v>
@@ -4232,23 +4286,23 @@
       <c r="C10" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="23" t="s">
         <v>70</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="H10" s="12" t="s">
         <v>136</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="J10" s="23" t="s">
         <v>139</v>
@@ -4264,31 +4318,31 @@
     </row>
     <row r="11" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="B11" s="12" t="s">
         <v>213</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>256</v>
-      </c>
-      <c r="D11" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="D11" s="23" t="s">
         <v>70</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="H11" s="12" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="I11" s="12" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="J11" s="23" t="s">
         <v>139</v>
@@ -4304,28 +4358,28 @@
     </row>
     <row r="12" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="B12" s="12" t="s">
         <v>213</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>263</v>
-      </c>
-      <c r="D12" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="D12" s="23" t="s">
         <v>70</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="F12" s="12" t="s">
         <v>125</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="H12" s="12" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="I12" s="12" t="s">
         <v>81</v>
@@ -4344,31 +4398,31 @@
     </row>
     <row r="13" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="B13" s="12" t="s">
         <v>213</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>268</v>
-      </c>
-      <c r="D13" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="D13" s="23" t="s">
         <v>70</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H13" s="12" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="I13" s="12" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="J13" s="23" t="s">
         <v>139</v>
@@ -4384,31 +4438,31 @@
     </row>
     <row r="14" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="B14" s="12" t="s">
         <v>213</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>275</v>
-      </c>
-      <c r="D14" s="12" t="s">
+        <v>267</v>
+      </c>
+      <c r="D14" s="23" t="s">
         <v>70</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="H14" s="12" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="I14" s="12" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="J14" s="23" t="s">
         <v>139</v>
@@ -4424,31 +4478,31 @@
     </row>
     <row r="15" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="B15" s="12" t="s">
         <v>213</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>282</v>
-      </c>
-      <c r="D15" s="12" t="s">
+        <v>274</v>
+      </c>
+      <c r="D15" s="23" t="s">
         <v>113</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="H15" s="12" t="s">
-        <v>286</v>
+        <v>552</v>
       </c>
       <c r="I15" s="12" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="J15" s="23" t="s">
         <v>139</v>
@@ -4464,31 +4518,31 @@
     </row>
     <row r="16" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="B16" s="12" t="s">
         <v>213</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>256</v>
-      </c>
-      <c r="D16" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="D16" s="23" t="s">
         <v>70</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="H16" s="12" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="I16" s="12" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="J16" s="23" t="s">
         <v>139</v>
@@ -4504,28 +4558,28 @@
     </row>
     <row r="17" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="B17" s="12" t="s">
         <v>213</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>263</v>
-      </c>
-      <c r="D17" s="12" t="s">
+        <v>255</v>
+      </c>
+      <c r="D17" s="23" t="s">
         <v>118</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F17" s="12" t="s">
         <v>125</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="H17" s="12" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="I17" s="12" t="s">
         <v>81</v>
@@ -4632,31 +4686,31 @@
     </row>
     <row r="3" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>54</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="J3" s="10" t="s">
         <v>128</v>
@@ -4672,31 +4726,31 @@
     </row>
     <row r="4" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="D4" s="10" t="s">
         <v>54</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="F4" s="8" t="s">
         <v>125</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="J4" s="10" t="s">
         <v>132</v>
@@ -4712,31 +4766,31 @@
     </row>
     <row r="5" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="D5" s="10" t="s">
         <v>54</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>125</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="J5" s="10" t="s">
         <v>132</v>
@@ -4752,31 +4806,31 @@
     </row>
     <row r="6" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="D6" s="10" t="s">
         <v>54</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>125</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="J6" s="10" t="s">
         <v>132</v>
@@ -4792,31 +4846,31 @@
     </row>
     <row r="7" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="D7" s="10" t="s">
         <v>54</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>125</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="J7" s="10" t="s">
         <v>132</v>
@@ -4832,31 +4886,31 @@
     </row>
     <row r="8" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="D8" s="10" t="s">
         <v>54</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>125</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="J8" s="10" t="s">
         <v>132</v>
@@ -4872,31 +4926,31 @@
     </row>
     <row r="9" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="D9" s="10" t="s">
         <v>54</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>125</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="J9" s="10" t="s">
         <v>132</v>
@@ -4912,31 +4966,31 @@
     </row>
     <row r="10" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="D10" s="10" t="s">
         <v>54</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="F10" s="8" t="s">
         <v>125</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
       <c r="J10" s="10" t="s">
         <v>132</v>
@@ -4952,31 +5006,31 @@
     </row>
     <row r="11" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="D11" s="10" t="s">
         <v>70</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="H11" s="8" t="s">
         <v>136</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="J11" s="10" t="s">
         <v>139</v>
@@ -4992,31 +5046,31 @@
     </row>
     <row r="12" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>70</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="J12" s="10" t="s">
         <v>139</v>
@@ -5032,28 +5086,28 @@
     </row>
     <row r="13" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="D13" s="10" t="s">
         <v>70</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>125</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="I13" s="8" t="s">
         <v>81</v>
@@ -5072,31 +5126,31 @@
     </row>
     <row r="14" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="D14" s="10" t="s">
         <v>70</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="J14" s="10" t="s">
         <v>139</v>
@@ -5112,31 +5166,31 @@
     </row>
     <row r="15" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="D15" s="10" t="s">
         <v>70</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="J15" s="10" t="s">
         <v>139</v>
@@ -5152,31 +5206,31 @@
     </row>
     <row r="16" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="D16" s="10" t="s">
         <v>113</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="J16" s="10" t="s">
         <v>139</v>
@@ -5192,31 +5246,31 @@
     </row>
     <row r="17" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="D17" s="10" t="s">
         <v>118</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>377</v>
+        <v>368</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="J17" s="10" t="s">
         <v>139</v>
@@ -5320,31 +5374,31 @@
     </row>
     <row r="3" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>54</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="F3" s="8" t="s">
         <v>72</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="J3" s="8" t="s">
         <v>128</v>
@@ -5360,31 +5414,31 @@
     </row>
     <row r="4" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>54</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="F4" s="8" t="s">
         <v>125</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="J4" s="8" t="s">
         <v>132</v>
@@ -5400,31 +5454,31 @@
     </row>
     <row r="5" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>54</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>125</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="J5" s="8" t="s">
         <v>132</v>
@@ -5440,31 +5494,31 @@
     </row>
     <row r="6" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>54</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>125</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="J6" s="8" t="s">
         <v>132</v>
@@ -5480,31 +5534,31 @@
     </row>
     <row r="7" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>54</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>125</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>401</v>
+        <v>392</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>402</v>
+        <v>393</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="J7" s="8" t="s">
         <v>132</v>
@@ -5520,31 +5574,31 @@
     </row>
     <row r="8" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>404</v>
+        <v>395</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>70</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>405</v>
+        <v>396</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>406</v>
+        <v>397</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>407</v>
+        <v>398</v>
       </c>
       <c r="H8" s="8" t="s">
         <v>136</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>408</v>
+        <v>399</v>
       </c>
       <c r="J8" s="8" t="s">
         <v>139</v>
@@ -5560,31 +5614,31 @@
     </row>
     <row r="9" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>410</v>
+        <v>401</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>70</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>411</v>
+        <v>402</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>412</v>
+        <v>403</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>413</v>
+        <v>404</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>414</v>
+        <v>405</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>415</v>
+        <v>406</v>
       </c>
       <c r="J9" s="8" t="s">
         <v>139</v>
@@ -5600,28 +5654,28 @@
     </row>
     <row r="10" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>416</v>
+        <v>407</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>417</v>
+        <v>408</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>70</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="F10" s="8" t="s">
         <v>125</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="I10" s="8" t="s">
         <v>81</v>
@@ -5640,31 +5694,31 @@
     </row>
     <row r="11" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>422</v>
+        <v>413</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>70</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>423</v>
+        <v>414</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>424</v>
+        <v>415</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>425</v>
+        <v>416</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>426</v>
+        <v>417</v>
       </c>
       <c r="J11" s="8" t="s">
         <v>139</v>
@@ -5680,31 +5734,31 @@
     </row>
     <row r="12" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>410</v>
+        <v>401</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>113</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>428</v>
+        <v>419</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>412</v>
+        <v>403</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>429</v>
+        <v>420</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>430</v>
+        <v>421</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>431</v>
+        <v>422</v>
       </c>
       <c r="J12" s="8" t="s">
         <v>139</v>
@@ -5720,31 +5774,31 @@
     </row>
     <row r="13" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>432</v>
+        <v>423</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>410</v>
+        <v>401</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>113</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>412</v>
+        <v>403</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>434</v>
+        <v>425</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>435</v>
+        <v>426</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>436</v>
+        <v>427</v>
       </c>
       <c r="J13" s="8" t="s">
         <v>139</v>
@@ -5760,31 +5814,31 @@
     </row>
     <row r="14" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>437</v>
+        <v>428</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>410</v>
+        <v>401</v>
       </c>
       <c r="D14" s="8" t="s">
         <v>113</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>438</v>
+        <v>429</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>412</v>
+        <v>403</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>439</v>
+        <v>430</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>440</v>
+        <v>431</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>441</v>
+        <v>432</v>
       </c>
       <c r="J14" s="8" t="s">
         <v>139</v>
@@ -5800,31 +5854,31 @@
     </row>
     <row r="15" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>442</v>
+        <v>433</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>410</v>
+        <v>401</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>444</v>
+        <v>435</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>412</v>
+        <v>403</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>445</v>
+        <v>436</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>447</v>
+        <v>438</v>
       </c>
       <c r="J15" s="8" t="s">
         <v>139</v>
@@ -5840,31 +5894,31 @@
     </row>
     <row r="16" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>448</v>
+        <v>439</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>410</v>
+        <v>401</v>
       </c>
       <c r="D16" s="8" t="s">
         <v>118</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>412</v>
+        <v>403</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>414</v>
+        <v>405</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>451</v>
+        <v>442</v>
       </c>
       <c r="J16" s="8" t="s">
         <v>139</v>
@@ -5880,28 +5934,28 @@
     </row>
     <row r="17" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>452</v>
+        <v>443</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>417</v>
+        <v>408</v>
       </c>
       <c r="D17" s="8" t="s">
         <v>118</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="F17" s="8" t="s">
         <v>125</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>454</v>
+        <v>445</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="I17" s="8" t="s">
         <v>81</v>
@@ -6008,31 +6062,31 @@
     </row>
     <row r="3" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>455</v>
+        <v>446</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>456</v>
+        <v>447</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>457</v>
+        <v>448</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>54</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>458</v>
+        <v>449</v>
       </c>
       <c r="F3" s="8" t="s">
         <v>125</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>459</v>
+        <v>450</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>460</v>
+        <v>451</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>461</v>
+        <v>452</v>
       </c>
       <c r="J3" s="8" t="s">
         <v>128</v>
@@ -6048,31 +6102,31 @@
     </row>
     <row r="4" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>456</v>
+        <v>447</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>457</v>
+        <v>448</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>54</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>463</v>
+        <v>454</v>
       </c>
       <c r="F4" s="8" t="s">
         <v>125</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>464</v>
+        <v>455</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>465</v>
+        <v>456</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>466</v>
+        <v>457</v>
       </c>
       <c r="J4" s="8" t="s">
         <v>132</v>
@@ -6088,31 +6142,31 @@
     </row>
     <row r="5" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>467</v>
+        <v>458</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>456</v>
+        <v>447</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>457</v>
+        <v>448</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>54</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>125</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>469</v>
+        <v>460</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>470</v>
+        <v>461</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>471</v>
+        <v>462</v>
       </c>
       <c r="J5" s="8" t="s">
         <v>132</v>
@@ -6128,31 +6182,31 @@
     </row>
     <row r="6" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>472</v>
+        <v>463</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>456</v>
+        <v>447</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>457</v>
+        <v>448</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>54</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>473</v>
+        <v>464</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>125</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>474</v>
+        <v>465</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>475</v>
+        <v>466</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>476</v>
+        <v>467</v>
       </c>
       <c r="J6" s="8" t="s">
         <v>132</v>
@@ -6168,31 +6222,31 @@
     </row>
     <row r="7" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>477</v>
+        <v>468</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>456</v>
+        <v>447</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>457</v>
+        <v>448</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>54</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>478</v>
+        <v>469</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>125</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>479</v>
+        <v>470</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
       <c r="J7" s="8" t="s">
         <v>132</v>
@@ -6208,31 +6262,31 @@
     </row>
     <row r="8" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>482</v>
+        <v>473</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>456</v>
+        <v>447</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>457</v>
+        <v>448</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>54</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>483</v>
+        <v>474</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>125</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>484</v>
+        <v>475</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>485</v>
+        <v>476</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>486</v>
+        <v>477</v>
       </c>
       <c r="J8" s="8" t="s">
         <v>132</v>
@@ -6248,31 +6302,31 @@
     </row>
     <row r="9" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>487</v>
+        <v>478</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>456</v>
+        <v>447</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>457</v>
+        <v>448</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>54</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>488</v>
+        <v>479</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>125</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>489</v>
+        <v>480</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>490</v>
+        <v>481</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>491</v>
+        <v>482</v>
       </c>
       <c r="J9" s="8" t="s">
         <v>132</v>
@@ -6288,31 +6342,31 @@
     </row>
     <row r="10" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>492</v>
+        <v>483</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>456</v>
+        <v>447</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>457</v>
+        <v>448</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>54</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>493</v>
+        <v>484</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>494</v>
+        <v>485</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>495</v>
+        <v>486</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>496</v>
+        <v>487</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>497</v>
+        <v>488</v>
       </c>
       <c r="J10" s="8" t="s">
         <v>132</v>
@@ -6328,31 +6382,31 @@
     </row>
     <row r="11" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>498</v>
+        <v>489</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>456</v>
+        <v>447</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>457</v>
+        <v>448</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>70</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>499</v>
+        <v>490</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>500</v>
+        <v>491</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>501</v>
+        <v>492</v>
       </c>
       <c r="H11" s="8" t="s">
         <v>136</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>502</v>
+        <v>493</v>
       </c>
       <c r="J11" s="8" t="s">
         <v>139</v>
@@ -6368,31 +6422,31 @@
     </row>
     <row r="12" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>503</v>
+        <v>494</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>456</v>
+        <v>447</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>504</v>
+        <v>495</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>70</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>505</v>
+        <v>496</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>506</v>
+        <v>497</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>507</v>
+        <v>498</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>508</v>
+        <v>499</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>509</v>
+        <v>500</v>
       </c>
       <c r="J12" s="8" t="s">
         <v>139</v>
@@ -6408,28 +6462,28 @@
     </row>
     <row r="13" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>510</v>
+        <v>501</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>456</v>
+        <v>447</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>511</v>
+        <v>502</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>70</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>125</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>514</v>
+        <v>505</v>
       </c>
       <c r="I13" s="8" t="s">
         <v>81</v>
@@ -6448,31 +6502,31 @@
     </row>
     <row r="14" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>515</v>
+        <v>506</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>456</v>
+        <v>447</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>516</v>
+        <v>507</v>
       </c>
       <c r="D14" s="8" t="s">
         <v>70</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>517</v>
+        <v>508</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>518</v>
+        <v>509</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>519</v>
+        <v>510</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>520</v>
+        <v>511</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="J14" s="8" t="s">
         <v>139</v>
@@ -6488,31 +6542,31 @@
     </row>
     <row r="15" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>522</v>
+        <v>513</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>456</v>
+        <v>447</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>523</v>
+        <v>514</v>
       </c>
       <c r="D15" s="8" t="s">
         <v>70</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>524</v>
+        <v>515</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>525</v>
+        <v>516</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>526</v>
+        <v>517</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>527</v>
+        <v>518</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>528</v>
+        <v>519</v>
       </c>
       <c r="J15" s="8" t="s">
         <v>139</v>
@@ -6528,31 +6582,31 @@
     </row>
     <row r="16" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>529</v>
+        <v>520</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>456</v>
+        <v>447</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>504</v>
+        <v>495</v>
       </c>
       <c r="D16" s="8" t="s">
         <v>113</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>530</v>
+        <v>521</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>506</v>
+        <v>497</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>531</v>
+        <v>522</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>532</v>
+        <v>523</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>533</v>
+        <v>524</v>
       </c>
       <c r="J16" s="8" t="s">
         <v>139</v>
@@ -6568,31 +6622,31 @@
     </row>
     <row r="17" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>534</v>
+        <v>525</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>456</v>
+        <v>447</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>535</v>
+        <v>526</v>
       </c>
       <c r="D17" s="8" t="s">
         <v>118</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>536</v>
+        <v>527</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>537</v>
+        <v>528</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>538</v>
+        <v>529</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>539</v>
+        <v>530</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>540</v>
+        <v>531</v>
       </c>
       <c r="J17" s="8" t="s">
         <v>139</v>

--- a/ShopFlow API testCase.xlsx
+++ b/ShopFlow API testCase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\QA Engineer\ShopFlow API\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB3EDE5D-AC21-4ECA-9C63-08FFC86987C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C314D69-3A93-48BC-A980-5170060816DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13740" tabRatio="650" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2445" yWindow="75" windowWidth="17010" windowHeight="11355" tabRatio="650" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Version History" sheetId="1" r:id="rId1"/>
@@ -22,12 +22,12 @@
     <sheet name="Carts" sheetId="7" r:id="rId7"/>
     <sheet name="Coupons" sheetId="8" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1177" uniqueCount="553">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1177" uniqueCount="554">
   <si>
     <t>Project Name</t>
   </si>
@@ -1012,9 +1012,6 @@
 3. Verify id in response</t>
   </si>
   <si>
-    <t>{"productId":1,"userId":2,"rating":5,"title":"Amazing product!","body":"Really loved every bit of it.","verified":true}</t>
-  </si>
-  <si>
     <t>Review submitted successfully</t>
   </si>
   <si>
@@ -1029,9 +1026,6 @@
 3. Verify error message</t>
   </si>
   <si>
-    <t>{"userId":1,"rating":4,"title":"Good","body":"Pretty decent product overall."}</t>
-  </si>
-  <si>
     <t>{"error":"productId is required"}</t>
   </si>
   <si>
@@ -1414,20 +1408,10 @@
     <t>TC_Carts_009</t>
   </si>
   <si>
-    <t>/api/carts?userId=1</t>
-  </si>
-  <si>
     <t>Filter cart by userId</t>
   </si>
   <si>
     <t>Cart for userId=1 exists</t>
-  </si>
-  <si>
-    <t>1. Send GET /api/carts?userId=1
-2. Verify result belongs to userId=1</t>
-  </si>
-  <si>
-    <t>Cart for userId=1 returned</t>
   </si>
   <si>
     <t>TC_Carts_010</t>
@@ -1951,6 +1935,38 @@
     <t>{
     "status":"shipped"
 }</t>
+  </si>
+  <si>
+    <t>{
+    "productId":1,
+    "userId":2,
+    "rating":5,
+    "title":"Amazing product!",
+    "body":"Really loved every bit of it.",
+    "verified":true
+}</t>
+  </si>
+  <si>
+    <t>{
+    "userId":2,
+    "rating":5,
+    "title":"Amazing product!",
+    "body":"Really loved every bit of it.",
+    "verified":true
+}</t>
+  </si>
+  <si>
+    <t>1. Send GET /api/carts?userId=1
+2. Verify result belongs to userId=2</t>
+  </si>
+  <si>
+    <t>userId = 2</t>
+  </si>
+  <si>
+    <t>Cart for userId=2 returned</t>
+  </si>
+  <si>
+    <t>/api/carts?userId=2</t>
   </si>
 </sst>
 </file>
@@ -3295,7 +3311,7 @@
         <v>125</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="H3" s="8" t="s">
         <v>126</v>
@@ -3337,19 +3353,19 @@
         <v>125</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="H4" s="8" t="s">
         <v>131</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="J4" s="25">
         <v>400</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="L4" s="24" t="s">
         <v>60</v>
@@ -3409,7 +3425,7 @@
         <v>122</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="D6" s="24" t="s">
         <v>70</v>
@@ -3418,22 +3434,22 @@
         <v>142</v>
       </c>
       <c r="F6" s="24" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="G6" s="24" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="J6" s="25" t="s">
         <v>139</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="L6" s="24" t="s">
         <v>60</v>
@@ -3709,10 +3725,10 @@
         <v>70</v>
       </c>
       <c r="E13" s="24" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
       <c r="F13" s="24" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="G13" s="24" t="s">
         <v>186</v>
@@ -3799,7 +3815,7 @@
         <v>143</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="H15" s="8" t="s">
         <v>199</v>
@@ -3841,7 +3857,7 @@
         <v>143</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="H16" s="8" t="s">
         <v>203</v>
@@ -4019,7 +4035,7 @@
         <v>217</v>
       </c>
       <c r="H3" s="12" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="I3" s="12" t="s">
         <v>218</v>
@@ -4059,7 +4075,7 @@
         <v>221</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="I4" s="12" t="s">
         <v>222</v>
@@ -4099,7 +4115,7 @@
         <v>225</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>548</v>
+        <v>543</v>
       </c>
       <c r="I5" s="12" t="s">
         <v>226</v>
@@ -4139,7 +4155,7 @@
         <v>229</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="I6" s="12" t="s">
         <v>230</v>
@@ -4179,7 +4195,7 @@
         <v>233</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="I7" s="12" t="s">
         <v>234</v>
@@ -4219,7 +4235,7 @@
         <v>237</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="I8" s="12" t="s">
         <v>238</v>
@@ -4259,10 +4275,10 @@
         <v>241</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="I9" s="12" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="J9" s="23" t="s">
         <v>132</v>
@@ -4499,7 +4515,7 @@
         <v>277</v>
       </c>
       <c r="H15" s="12" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="I15" s="12" t="s">
         <v>278</v>
@@ -4684,7 +4700,7 @@
       <c r="M2" s="5"/>
       <c r="N2" s="5"/>
     </row>
-    <row r="3" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" ht="124.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>286</v>
       </c>
@@ -4707,10 +4723,10 @@
         <v>291</v>
       </c>
       <c r="H3" s="8" t="s">
+        <v>548</v>
+      </c>
+      <c r="I3" s="8" t="s">
         <v>292</v>
-      </c>
-      <c r="I3" s="8" t="s">
-        <v>293</v>
       </c>
       <c r="J3" s="10" t="s">
         <v>128</v>
@@ -4724,9 +4740,9 @@
       </c>
       <c r="N3" s="8"/>
     </row>
-    <row r="4" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" ht="120.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>287</v>
@@ -4738,19 +4754,19 @@
         <v>54</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F4" s="8" t="s">
         <v>125</v>
       </c>
       <c r="G4" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>549</v>
+      </c>
+      <c r="I4" s="8" t="s">
         <v>296</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>297</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>298</v>
       </c>
       <c r="J4" s="10" t="s">
         <v>132</v>
@@ -4766,7 +4782,7 @@
     </row>
     <row r="5" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B5" s="8" t="s">
         <v>287</v>
@@ -4778,16 +4794,16 @@
         <v>54</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>125</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="I5" s="8" t="s">
         <v>222</v>
@@ -4806,7 +4822,7 @@
     </row>
     <row r="6" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>287</v>
@@ -4818,19 +4834,19 @@
         <v>54</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>125</v>
       </c>
       <c r="G6" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="I6" s="8" t="s">
         <v>305</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>306</v>
-      </c>
-      <c r="I6" s="8" t="s">
-        <v>307</v>
       </c>
       <c r="J6" s="10" t="s">
         <v>132</v>
@@ -4846,7 +4862,7 @@
     </row>
     <row r="7" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B7" s="8" t="s">
         <v>287</v>
@@ -4858,19 +4874,19 @@
         <v>54</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>125</v>
       </c>
       <c r="G7" s="8" t="s">
+        <v>308</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="I7" s="8" t="s">
         <v>310</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>311</v>
-      </c>
-      <c r="I7" s="8" t="s">
-        <v>312</v>
       </c>
       <c r="J7" s="10" t="s">
         <v>132</v>
@@ -4886,7 +4902,7 @@
     </row>
     <row r="8" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B8" s="8" t="s">
         <v>287</v>
@@ -4898,19 +4914,19 @@
         <v>54</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>125</v>
       </c>
       <c r="G8" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>314</v>
+      </c>
+      <c r="I8" s="8" t="s">
         <v>315</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="I8" s="8" t="s">
-        <v>317</v>
       </c>
       <c r="J8" s="10" t="s">
         <v>132</v>
@@ -4926,7 +4942,7 @@
     </row>
     <row r="9" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B9" s="8" t="s">
         <v>287</v>
@@ -4938,19 +4954,19 @@
         <v>54</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>125</v>
       </c>
       <c r="G9" s="8" t="s">
+        <v>318</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="I9" s="8" t="s">
         <v>320</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>321</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>322</v>
       </c>
       <c r="J9" s="10" t="s">
         <v>132</v>
@@ -4966,7 +4982,7 @@
     </row>
     <row r="10" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B10" s="8" t="s">
         <v>287</v>
@@ -4978,19 +4994,19 @@
         <v>54</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="F10" s="8" t="s">
         <v>125</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="J10" s="10" t="s">
         <v>132</v>
@@ -5006,7 +5022,7 @@
     </row>
     <row r="11" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>287</v>
@@ -5018,19 +5034,19 @@
         <v>70</v>
       </c>
       <c r="E11" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="G11" s="8" t="s">
         <v>328</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>329</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>330</v>
       </c>
       <c r="H11" s="8" t="s">
         <v>136</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="J11" s="10" t="s">
         <v>139</v>
@@ -5046,31 +5062,31 @@
     </row>
     <row r="12" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B12" s="8" t="s">
         <v>287</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D12" s="10" t="s">
         <v>70</v>
       </c>
       <c r="E12" s="8" t="s">
+        <v>332</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="G12" s="8" t="s">
         <v>334</v>
       </c>
-      <c r="F12" s="8" t="s">
+      <c r="H12" s="8" t="s">
         <v>335</v>
       </c>
-      <c r="G12" s="8" t="s">
+      <c r="I12" s="8" t="s">
         <v>336</v>
-      </c>
-      <c r="H12" s="8" t="s">
-        <v>337</v>
-      </c>
-      <c r="I12" s="8" t="s">
-        <v>338</v>
       </c>
       <c r="J12" s="10" t="s">
         <v>139</v>
@@ -5086,28 +5102,28 @@
     </row>
     <row r="13" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B13" s="8" t="s">
         <v>287</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D13" s="10" t="s">
         <v>70</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>125</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="I13" s="8" t="s">
         <v>81</v>
@@ -5126,31 +5142,31 @@
     </row>
     <row r="14" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B14" s="8" t="s">
         <v>287</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D14" s="10" t="s">
         <v>70</v>
       </c>
       <c r="E14" s="8" t="s">
+        <v>344</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>345</v>
+      </c>
+      <c r="G14" s="8" t="s">
         <v>346</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="H14" s="8" t="s">
         <v>347</v>
       </c>
-      <c r="G14" s="8" t="s">
+      <c r="I14" s="8" t="s">
         <v>348</v>
-      </c>
-      <c r="H14" s="8" t="s">
-        <v>349</v>
-      </c>
-      <c r="I14" s="8" t="s">
-        <v>350</v>
       </c>
       <c r="J14" s="10" t="s">
         <v>139</v>
@@ -5166,31 +5182,31 @@
     </row>
     <row r="15" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B15" s="8" t="s">
         <v>287</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="D15" s="10" t="s">
         <v>70</v>
       </c>
       <c r="E15" s="8" t="s">
+        <v>351</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>352</v>
+      </c>
+      <c r="G15" s="8" t="s">
         <v>353</v>
       </c>
-      <c r="F15" s="8" t="s">
+      <c r="H15" s="8" t="s">
         <v>354</v>
       </c>
-      <c r="G15" s="8" t="s">
+      <c r="I15" s="8" t="s">
         <v>355</v>
-      </c>
-      <c r="H15" s="8" t="s">
-        <v>356</v>
-      </c>
-      <c r="I15" s="8" t="s">
-        <v>357</v>
       </c>
       <c r="J15" s="10" t="s">
         <v>139</v>
@@ -5206,31 +5222,31 @@
     </row>
     <row r="16" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B16" s="8" t="s">
         <v>287</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D16" s="10" t="s">
         <v>113</v>
       </c>
       <c r="E16" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="H16" s="8" t="s">
         <v>359</v>
       </c>
-      <c r="F16" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="G16" s="8" t="s">
+      <c r="I16" s="8" t="s">
         <v>360</v>
-      </c>
-      <c r="H16" s="8" t="s">
-        <v>361</v>
-      </c>
-      <c r="I16" s="8" t="s">
-        <v>362</v>
       </c>
       <c r="J16" s="10" t="s">
         <v>139</v>
@@ -5246,31 +5262,31 @@
     </row>
     <row r="17" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B17" s="8" t="s">
         <v>287</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="D17" s="10" t="s">
         <v>118</v>
       </c>
       <c r="E17" s="8" t="s">
+        <v>363</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>364</v>
+      </c>
+      <c r="G17" s="8" t="s">
         <v>365</v>
       </c>
-      <c r="F17" s="8" t="s">
+      <c r="H17" s="8" t="s">
         <v>366</v>
       </c>
-      <c r="G17" s="8" t="s">
+      <c r="I17" s="8" t="s">
         <v>367</v>
-      </c>
-      <c r="H17" s="8" t="s">
-        <v>368</v>
-      </c>
-      <c r="I17" s="8" t="s">
-        <v>369</v>
       </c>
       <c r="J17" s="10" t="s">
         <v>139</v>
@@ -5374,31 +5390,31 @@
     </row>
     <row r="3" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
+        <v>368</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>369</v>
+      </c>
+      <c r="C3" s="8" t="s">
         <v>370</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>371</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>372</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>54</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="F3" s="8" t="s">
         <v>72</v>
       </c>
       <c r="G3" s="8" t="s">
+        <v>372</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>373</v>
+      </c>
+      <c r="I3" s="8" t="s">
         <v>374</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>375</v>
-      </c>
-      <c r="I3" s="8" t="s">
-        <v>376</v>
       </c>
       <c r="J3" s="8" t="s">
         <v>128</v>
@@ -5414,28 +5430,28 @@
     </row>
     <row r="4" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>54</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="F4" s="8" t="s">
         <v>125</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="I4" s="8" t="s">
         <v>222</v>
@@ -5454,28 +5470,28 @@
     </row>
     <row r="5" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>54</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>125</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="I5" s="8" t="s">
         <v>234</v>
@@ -5494,31 +5510,31 @@
     </row>
     <row r="6" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>54</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>125</v>
       </c>
       <c r="G6" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>386</v>
+      </c>
+      <c r="I6" s="8" t="s">
         <v>387</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>388</v>
-      </c>
-      <c r="I6" s="8" t="s">
-        <v>389</v>
       </c>
       <c r="J6" s="8" t="s">
         <v>132</v>
@@ -5534,31 +5550,31 @@
     </row>
     <row r="7" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>54</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>125</v>
       </c>
       <c r="G7" s="8" t="s">
+        <v>390</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>391</v>
+      </c>
+      <c r="I7" s="8" t="s">
         <v>392</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>393</v>
-      </c>
-      <c r="I7" s="8" t="s">
-        <v>394</v>
       </c>
       <c r="J7" s="8" t="s">
         <v>132</v>
@@ -5574,31 +5590,31 @@
     </row>
     <row r="8" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>70</v>
       </c>
       <c r="E8" s="8" t="s">
+        <v>394</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>395</v>
+      </c>
+      <c r="G8" s="8" t="s">
         <v>396</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>397</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>398</v>
       </c>
       <c r="H8" s="8" t="s">
         <v>136</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="J8" s="8" t="s">
         <v>139</v>
@@ -5614,31 +5630,31 @@
     </row>
     <row r="9" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>70</v>
       </c>
       <c r="E9" s="8" t="s">
+        <v>400</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>401</v>
+      </c>
+      <c r="G9" s="8" t="s">
         <v>402</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="H9" s="8" t="s">
         <v>403</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="I9" s="8" t="s">
         <v>404</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>405</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>406</v>
       </c>
       <c r="J9" s="8" t="s">
         <v>139</v>
@@ -5654,28 +5670,28 @@
     </row>
     <row r="10" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>70</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="F10" s="8" t="s">
         <v>125</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="I10" s="8" t="s">
         <v>81</v>
@@ -5694,31 +5710,31 @@
     </row>
     <row r="11" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>413</v>
+        <v>553</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>70</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>416</v>
+        <v>550</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>264</v>
+        <v>551</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>417</v>
+        <v>552</v>
       </c>
       <c r="J11" s="8" t="s">
         <v>139</v>
@@ -5734,31 +5750,31 @@
     </row>
     <row r="12" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>113</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="J12" s="8" t="s">
         <v>139</v>
@@ -5774,31 +5790,31 @@
     </row>
     <row r="13" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>113</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="J13" s="8" t="s">
         <v>139</v>
@@ -5814,31 +5830,31 @@
     </row>
     <row r="14" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D14" s="8" t="s">
         <v>113</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="J14" s="8" t="s">
         <v>139</v>
@@ -5854,31 +5870,31 @@
     </row>
     <row r="15" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
+        <v>428</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>369</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>399</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>429</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>430</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>401</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>431</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>432</v>
+      </c>
+      <c r="I15" s="8" t="s">
         <v>433</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>371</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>401</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>434</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>435</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>403</v>
-      </c>
-      <c r="G15" s="8" t="s">
-        <v>436</v>
-      </c>
-      <c r="H15" s="8" t="s">
-        <v>437</v>
-      </c>
-      <c r="I15" s="8" t="s">
-        <v>438</v>
       </c>
       <c r="J15" s="8" t="s">
         <v>139</v>
@@ -5894,31 +5910,31 @@
     </row>
     <row r="16" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D16" s="8" t="s">
         <v>118</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="F16" s="8" t="s">
+        <v>401</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>436</v>
+      </c>
+      <c r="H16" s="8" t="s">
         <v>403</v>
       </c>
-      <c r="G16" s="8" t="s">
-        <v>441</v>
-      </c>
-      <c r="H16" s="8" t="s">
-        <v>405</v>
-      </c>
       <c r="I16" s="8" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="J16" s="8" t="s">
         <v>139</v>
@@ -5934,28 +5950,28 @@
     </row>
     <row r="17" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D17" s="8" t="s">
         <v>118</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="F17" s="8" t="s">
         <v>125</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="I17" s="8" t="s">
         <v>81</v>
@@ -6062,31 +6078,31 @@
     </row>
     <row r="3" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>54</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="F3" s="8" t="s">
         <v>125</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="J3" s="8" t="s">
         <v>128</v>
@@ -6102,31 +6118,31 @@
     </row>
     <row r="4" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>54</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="F4" s="8" t="s">
         <v>125</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="J4" s="8" t="s">
         <v>132</v>
@@ -6142,31 +6158,31 @@
     </row>
     <row r="5" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>54</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>125</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="J5" s="8" t="s">
         <v>132</v>
@@ -6182,31 +6198,31 @@
     </row>
     <row r="6" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>54</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>125</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="J6" s="8" t="s">
         <v>132</v>
@@ -6222,31 +6238,31 @@
     </row>
     <row r="7" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>54</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>125</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="J7" s="8" t="s">
         <v>132</v>
@@ -6262,31 +6278,31 @@
     </row>
     <row r="8" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>54</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>125</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="J8" s="8" t="s">
         <v>132</v>
@@ -6302,31 +6318,31 @@
     </row>
     <row r="9" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>54</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>125</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="J9" s="8" t="s">
         <v>132</v>
@@ -6342,31 +6358,31 @@
     </row>
     <row r="10" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>54</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="J10" s="8" t="s">
         <v>132</v>
@@ -6382,31 +6398,31 @@
     </row>
     <row r="11" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>70</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="H11" s="8" t="s">
         <v>136</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="J11" s="8" t="s">
         <v>139</v>
@@ -6422,31 +6438,31 @@
     </row>
     <row r="12" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>70</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="J12" s="8" t="s">
         <v>139</v>
@@ -6462,28 +6478,28 @@
     </row>
     <row r="13" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>70</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>125</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="I13" s="8" t="s">
         <v>81</v>
@@ -6502,31 +6518,31 @@
     </row>
     <row r="14" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="D14" s="8" t="s">
         <v>70</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="J14" s="8" t="s">
         <v>139</v>
@@ -6542,31 +6558,31 @@
     </row>
     <row r="15" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="D15" s="8" t="s">
         <v>70</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="J15" s="8" t="s">
         <v>139</v>
@@ -6582,31 +6598,31 @@
     </row>
     <row r="16" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="D16" s="8" t="s">
         <v>113</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="J16" s="8" t="s">
         <v>139</v>
@@ -6622,31 +6638,31 @@
     </row>
     <row r="17" spans="1:14" ht="51.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="D17" s="8" t="s">
         <v>118</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="J17" s="8" t="s">
         <v>139</v>
